--- a/docs/GaelGunStore_B42_checklist.xlsx
+++ b/docs/GaelGunStore_B42_checklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armas" sheetId="1" r:id="Rc9664efb5c774be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armas" sheetId="1" r:id="R44a274d89f604d52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -370,211 +370,211 @@
     <x:t xml:space="preserve">Springfield XD Pistol</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Base.Anaconda</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Anaconda 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Revólveres</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">—</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.ColtNavy1851</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ColtNavy1851 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">base:bullets_38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.ColtNavyExorcist</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ColtNavyExorcist 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.ColtPeacemaker1873</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ColtPeacemaker1873 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.MP_R8</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MP_R8 357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Nagant_M1895</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Nagant_M1895 22LR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Python357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Python .357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Revolver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Revolver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Revolver38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Revolver38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Revolver666</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Revolver666 22LR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Revolver_long</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Revolver_long</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Revolver_short</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Revolver_short</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Rhino20DS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rhino20DS 357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Rhino60DS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rhino60DS</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.RSH12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RSH12 308</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">base:bullets_308</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Ruger357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ruger357 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Schofield1875</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Schofield1875 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.ScrapRevolver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">ScrapRevolver 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Snub22LR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Snub22LR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.SW1905</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SW1905 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.SW1917</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SW1917 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.SW500</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SW500 50Magnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.SW629</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Smith&amp;Wesson M629</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.SWM3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SWM3 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.SWM327</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SWM327 357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.SWM629_Deluxe</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SWM629_Deluxe 44</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Taurus606</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taurus606 357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Taurus_raging_bull</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taurus_raging_bull 357</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Taurus_raging_bull460</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taurus_raging_bull460 50Magnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Taurus_RT85</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Taurus_RT85 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Webley_MK_snub</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Webley_MK_snub 38</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Webley_Revolver</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Webley_Revolver 38</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">☐</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Anaconda</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Anaconda 44</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Revólveres</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">—</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.ColtNavy1851</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ColtNavy1851 38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">base:bullets_38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.ColtNavyExorcist</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ColtNavyExorcist 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.ColtPeacemaker1873</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ColtPeacemaker1873 45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.MP_R8</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MP_R8 357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Nagant_M1895</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Nagant_M1895 22LR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Python357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Python .357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Revolver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Revolver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Revolver38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Revolver38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Revolver666</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Revolver666 22LR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Revolver_long</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Revolver_long</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Revolver_short</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Revolver_short</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Rhino20DS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rhino20DS 357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Rhino60DS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rhino60DS</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.RSH12</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RSH12 308</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">base:bullets_308</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Ruger357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Ruger357 45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Schofield1875</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Schofield1875 44</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.ScrapRevolver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ScrapRevolver 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Snub22LR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Snub22LR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.SW1905</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SW1905 38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.SW1917</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SW1917 45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.SW500</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SW500 50Magnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.SW629</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Smith&amp;Wesson M629</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.SWM3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SWM3 38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.SWM327</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SWM327 357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.SWM629_Deluxe</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SWM629_Deluxe 44</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Taurus606</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Taurus606 357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Taurus_raging_bull</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Taurus_raging_bull 357</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Taurus_raging_bull460</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Taurus_raging_bull460 50Magnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Taurus_RT85</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Taurus_RT85 38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Webley_MK_snub</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Webley_MK_snub 38</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Webley_Revolver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Webley_Revolver 38</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Base.AEK919</x:t>
@@ -2985,7 +2985,7 @@
       </x:c>
       <x:c r="E3" s="5" t="n">
         <x:f>COUNTIF(B7:B381,"☑")+COUNTIF(B7:B381,"Hecho/Automatizado")</x:f>
-        <x:v>76</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F3" s="1"/>
       <x:c r="G3" s="4" t="s">
@@ -2993,7 +2993,7 @@
       </x:c>
       <x:c r="H3" s="5" t="n">
         <x:f>B3-E3</x:f>
-        <x:v>299</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="I3" s="1"/>
       <x:c r="J3" s="1"/>
@@ -8169,23 +8169,23 @@
       <x:c r="A54" s="9">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="B54" s="11" t="s">
+      <x:c r="B54" s="11" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="C54" s="1" t="s">
+      <x:c r="D54" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D54" s="1" t="s">
+      <x:c r="E54" s="12" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="E54" s="12" t="s">
+      <x:c r="F54" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F54" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H54" s="1" t="s">
         <x:v>25</x:v>
@@ -8193,7 +8193,9 @@
       <x:c r="I54" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J54" s="1"/>
+      <x:c r="J54" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K54" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -8274,31 +8276,33 @@
       <x:c r="A55" s="9">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B55" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B55" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D55" s="1" t="s">
+      <x:c r="E55" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G55" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H55" s="1" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="E55" s="12" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F55" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G55" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H55" s="1" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="I55" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J55" s="1"/>
+      <x:c r="J55" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K55" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -8379,23 +8383,23 @@
       <x:c r="A56" s="9">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B56" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B56" s="11" t="str">
+        <x:v>☐</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="D56" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
       <x:c r="E56" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F56" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H56" s="1" t="s">
         <x:v>31</x:v>
@@ -8403,7 +8407,9 @@
       <x:c r="I56" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J56" s="1"/>
+      <x:c r="J56" s="1" t="str">
+        <x:v>Sin perfil ADS personal guardado</x:v>
+      </x:c>
       <x:c r="K56" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -8484,23 +8490,23 @@
       <x:c r="A57" s="9">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B57" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B57" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="D57" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
       <x:c r="E57" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F57" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H57" s="1" t="s">
         <x:v>51</x:v>
@@ -8508,7 +8514,9 @@
       <x:c r="I57" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J57" s="1"/>
+      <x:c r="J57" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K57" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -8589,23 +8597,23 @@
       <x:c r="A58" s="9">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B58" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B58" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
       <x:c r="E58" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F58" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F58" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H58" s="1" t="s">
         <x:v>21</x:v>
@@ -8613,7 +8621,9 @@
       <x:c r="I58" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J58" s="1"/>
+      <x:c r="J58" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K58" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -8694,23 +8704,23 @@
       <x:c r="A59" s="9">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B59" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B59" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>135</x:v>
-      </x:c>
       <x:c r="E59" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F59" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F59" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H59" s="1" t="s">
         <x:v>48</x:v>
@@ -8718,7 +8728,9 @@
       <x:c r="I59" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J59" s="1"/>
+      <x:c r="J59" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K59" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -8799,23 +8811,23 @@
       <x:c r="A60" s="9">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B60" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B60" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
         <x:v>136</x:v>
       </x:c>
-      <x:c r="D60" s="1" t="s">
-        <x:v>137</x:v>
-      </x:c>
       <x:c r="E60" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F60" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F60" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H60" s="1" t="s">
         <x:v>21</x:v>
@@ -8823,7 +8835,9 @@
       <x:c r="I60" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J60" s="1"/>
+      <x:c r="J60" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K60" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -8904,23 +8918,23 @@
       <x:c r="A61" s="9">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B61" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B61" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="D61" s="1" t="s">
-        <x:v>139</x:v>
-      </x:c>
       <x:c r="E61" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F61" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H61" s="1" t="s">
         <x:v>51</x:v>
@@ -8928,7 +8942,9 @@
       <x:c r="I61" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J61" s="1"/>
+      <x:c r="J61" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K61" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9009,31 +9025,33 @@
       <x:c r="A62" s="9">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B62" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B62" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
-      <x:c r="D62" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
       <x:c r="E62" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F62" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F62" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H62" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I62" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J62" s="1"/>
+      <x:c r="J62" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K62" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9114,23 +9132,23 @@
       <x:c r="A63" s="9">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B63" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B63" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D63" s="1" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="D63" s="1" t="s">
-        <x:v>143</x:v>
-      </x:c>
       <x:c r="E63" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F63" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F63" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H63" s="1" t="s">
         <x:v>48</x:v>
@@ -9138,7 +9156,9 @@
       <x:c r="I63" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J63" s="1"/>
+      <x:c r="J63" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K63" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9219,23 +9239,23 @@
       <x:c r="A64" s="9">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B64" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B64" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="D64" s="1" t="s">
-        <x:v>145</x:v>
-      </x:c>
       <x:c r="E64" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F64" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F64" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H64" s="1" t="s">
         <x:v>21</x:v>
@@ -9243,7 +9263,9 @@
       <x:c r="I64" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J64" s="1"/>
+      <x:c r="J64" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K64" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9324,31 +9346,33 @@
       <x:c r="A65" s="9">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B65" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B65" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>147</x:v>
-      </x:c>
       <x:c r="E65" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F65" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F65" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H65" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I65" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J65" s="1"/>
+      <x:c r="J65" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K65" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9429,23 +9453,23 @@
       <x:c r="A66" s="9">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B66" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B66" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D66" s="1" t="s">
         <x:v>148</x:v>
       </x:c>
-      <x:c r="D66" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
       <x:c r="E66" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F66" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F66" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H66" s="1" t="s">
         <x:v>21</x:v>
@@ -9453,7 +9477,9 @@
       <x:c r="I66" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J66" s="1"/>
+      <x:c r="J66" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K66" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9534,23 +9560,23 @@
       <x:c r="A67" s="9">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B67" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B67" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>151</x:v>
-      </x:c>
       <x:c r="E67" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F67" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F67" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H67" s="1" t="s">
         <x:v>21</x:v>
@@ -9558,7 +9584,9 @@
       <x:c r="I67" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J67" s="1"/>
+      <x:c r="J67" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K67" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9639,31 +9667,33 @@
       <x:c r="A68" s="9">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B68" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B68" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="D68" s="1" t="s">
+      <x:c r="E68" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F68" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="G68" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H68" s="1" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="E68" s="12" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="F68" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="G68" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="H68" s="1" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="I68" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J68" s="1"/>
+      <x:c r="J68" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K68" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9744,23 +9774,23 @@
       <x:c r="A69" s="9">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B69" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B69" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
         <x:v>155</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="s">
-        <x:v>156</x:v>
-      </x:c>
       <x:c r="E69" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F69" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F69" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H69" s="1" t="s">
         <x:v>51</x:v>
@@ -9768,7 +9798,9 @@
       <x:c r="I69" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J69" s="1"/>
+      <x:c r="J69" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K69" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9849,23 +9881,23 @@
       <x:c r="A70" s="9">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B70" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B70" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="D70" s="1" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="D70" s="1" t="s">
-        <x:v>158</x:v>
-      </x:c>
       <x:c r="E70" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F70" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F70" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H70" s="1" t="s">
         <x:v>25</x:v>
@@ -9873,7 +9905,9 @@
       <x:c r="I70" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J70" s="1"/>
+      <x:c r="J70" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K70" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -9954,23 +9988,23 @@
       <x:c r="A71" s="9">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B71" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B71" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="D71" s="1" t="s">
-        <x:v>160</x:v>
-      </x:c>
       <x:c r="E71" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F71" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F71" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H71" s="1" t="s">
         <x:v>31</x:v>
@@ -9978,7 +10012,9 @@
       <x:c r="I71" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J71" s="1"/>
+      <x:c r="J71" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K71" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10059,23 +10095,23 @@
       <x:c r="A72" s="9">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="B72" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B72" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D72" s="1" t="s">
         <x:v>161</x:v>
       </x:c>
-      <x:c r="D72" s="1" t="s">
-        <x:v>162</x:v>
-      </x:c>
       <x:c r="E72" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F72" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F72" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H72" s="1" t="s">
         <x:v>48</x:v>
@@ -10083,7 +10119,9 @@
       <x:c r="I72" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J72" s="1"/>
+      <x:c r="J72" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K72" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10164,31 +10202,33 @@
       <x:c r="A73" s="9">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B73" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B73" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="D73" s="1" t="s">
-        <x:v>164</x:v>
-      </x:c>
       <x:c r="E73" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F73" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F73" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H73" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I73" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J73" s="1"/>
+      <x:c r="J73" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K73" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10269,23 +10309,23 @@
       <x:c r="A74" s="9">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B74" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B74" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="D74" s="1" t="s">
         <x:v>165</x:v>
       </x:c>
-      <x:c r="D74" s="1" t="s">
-        <x:v>166</x:v>
-      </x:c>
       <x:c r="E74" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F74" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F74" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H74" s="1" t="s">
         <x:v>51</x:v>
@@ -10293,7 +10333,9 @@
       <x:c r="I74" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J74" s="1"/>
+      <x:c r="J74" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K74" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10374,23 +10416,23 @@
       <x:c r="A75" s="9">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B75" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B75" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="D75" s="1" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="D75" s="1" t="s">
-        <x:v>168</x:v>
-      </x:c>
       <x:c r="E75" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F75" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F75" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H75" s="1" t="s">
         <x:v>28</x:v>
@@ -10398,7 +10440,9 @@
       <x:c r="I75" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J75" s="1"/>
+      <x:c r="J75" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K75" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10479,23 +10523,23 @@
       <x:c r="A76" s="9">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B76" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B76" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="D76" s="1" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="D76" s="1" t="s">
-        <x:v>170</x:v>
-      </x:c>
       <x:c r="E76" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F76" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F76" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H76" s="1" t="s">
         <x:v>25</x:v>
@@ -10503,7 +10547,9 @@
       <x:c r="I76" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J76" s="1"/>
+      <x:c r="J76" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K76" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10584,31 +10630,33 @@
       <x:c r="A77" s="9">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B77" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B77" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="D77" s="1" t="s">
-        <x:v>172</x:v>
-      </x:c>
       <x:c r="E77" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F77" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F77" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H77" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I77" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J77" s="1"/>
+      <x:c r="J77" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K77" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10689,23 +10737,23 @@
       <x:c r="A78" s="9">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B78" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B78" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="D78" s="1" t="s">
-        <x:v>174</x:v>
-      </x:c>
       <x:c r="E78" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F78" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F78" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H78" s="1" t="s">
         <x:v>21</x:v>
@@ -10713,7 +10761,9 @@
       <x:c r="I78" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J78" s="1"/>
+      <x:c r="J78" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K78" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10794,23 +10844,23 @@
       <x:c r="A79" s="9">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="B79" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B79" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="D79" s="1" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="D79" s="1" t="s">
-        <x:v>176</x:v>
-      </x:c>
       <x:c r="E79" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F79" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F79" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H79" s="1" t="s">
         <x:v>25</x:v>
@@ -10818,7 +10868,9 @@
       <x:c r="I79" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J79" s="1"/>
+      <x:c r="J79" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K79" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -10899,23 +10951,23 @@
       <x:c r="A80" s="9">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="B80" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B80" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="D80" s="1" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="D80" s="1" t="s">
-        <x:v>178</x:v>
-      </x:c>
       <x:c r="E80" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F80" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F80" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H80" s="1" t="s">
         <x:v>21</x:v>
@@ -10923,7 +10975,9 @@
       <x:c r="I80" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J80" s="1"/>
+      <x:c r="J80" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K80" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -11004,23 +11058,23 @@
       <x:c r="A81" s="9">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B81" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B81" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
         <x:v>179</x:v>
       </x:c>
-      <x:c r="D81" s="1" t="s">
-        <x:v>180</x:v>
-      </x:c>
       <x:c r="E81" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F81" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F81" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H81" s="1" t="s">
         <x:v>21</x:v>
@@ -11028,7 +11082,9 @@
       <x:c r="I81" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J81" s="1"/>
+      <x:c r="J81" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K81" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -11109,23 +11165,23 @@
       <x:c r="A82" s="9">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B82" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B82" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
         <x:v>181</x:v>
       </x:c>
-      <x:c r="D82" s="1" t="s">
-        <x:v>182</x:v>
-      </x:c>
       <x:c r="E82" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F82" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F82" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H82" s="1" t="s">
         <x:v>28</x:v>
@@ -11133,7 +11189,9 @@
       <x:c r="I82" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J82" s="1"/>
+      <x:c r="J82" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K82" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -11214,31 +11272,33 @@
       <x:c r="A83" s="9">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="B83" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B83" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D83" s="1" t="s">
-        <x:v>184</x:v>
-      </x:c>
       <x:c r="E83" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F83" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F83" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H83" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I83" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J83" s="1"/>
+      <x:c r="J83" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K83" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -11319,31 +11379,33 @@
       <x:c r="A84" s="9">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B84" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B84" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D84" s="1" t="s">
-        <x:v>186</x:v>
-      </x:c>
       <x:c r="E84" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F84" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F84" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H84" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I84" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J84" s="1"/>
+      <x:c r="J84" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K84" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -11424,31 +11486,33 @@
       <x:c r="A85" s="9">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B85" s="11" t="s">
-        <x:v>120</x:v>
+      <x:c r="B85" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="D85" s="1" t="s">
         <x:v>187</x:v>
       </x:c>
-      <x:c r="D85" s="1" t="s">
-        <x:v>188</x:v>
-      </x:c>
       <x:c r="E85" s="12" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="F85" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
-      <x:c r="F85" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H85" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="I85" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J85" s="1"/>
+      <x:c r="J85" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K85" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -11530,7 +11594,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B86" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
         <x:v>189</x:v>
@@ -11635,7 +11699,7 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B87" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
         <x:v>194</x:v>
@@ -11740,7 +11804,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B88" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
         <x:v>196</x:v>
@@ -11845,7 +11909,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B89" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
         <x:v>198</x:v>
@@ -11950,7 +12014,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B90" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
         <x:v>200</x:v>
@@ -12055,7 +12119,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B91" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
         <x:v>202</x:v>
@@ -12160,7 +12224,7 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B92" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
         <x:v>204</x:v>
@@ -12265,7 +12329,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B93" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
         <x:v>206</x:v>
@@ -12370,7 +12434,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B94" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>208</x:v>
@@ -12475,7 +12539,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B95" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>210</x:v>
@@ -12580,7 +12644,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B96" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
         <x:v>212</x:v>
@@ -12685,7 +12749,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B97" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
         <x:v>214</x:v>
@@ -12790,7 +12854,7 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B98" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>216</x:v>
@@ -12895,7 +12959,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B99" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
         <x:v>218</x:v>
@@ -13000,7 +13064,7 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B100" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
         <x:v>220</x:v>
@@ -13105,7 +13169,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B101" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
         <x:v>222</x:v>
@@ -13210,7 +13274,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B102" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
         <x:v>224</x:v>
@@ -13315,7 +13379,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B103" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
         <x:v>227</x:v>
@@ -13420,7 +13484,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B104" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
         <x:v>229</x:v>
@@ -13525,7 +13589,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B105" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
         <x:v>231</x:v>
@@ -13630,7 +13694,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B106" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
         <x:v>233</x:v>
@@ -13735,7 +13799,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B107" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
         <x:v>235</x:v>
@@ -13840,7 +13904,7 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B108" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
         <x:v>237</x:v>
@@ -13945,7 +14009,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B109" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
         <x:v>239</x:v>
@@ -14050,7 +14114,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B110" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
         <x:v>241</x:v>
@@ -14155,7 +14219,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B111" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
         <x:v>243</x:v>
@@ -14260,7 +14324,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B112" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
         <x:v>245</x:v>
@@ -14365,7 +14429,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B113" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
         <x:v>247</x:v>
@@ -14470,7 +14534,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B114" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
         <x:v>249</x:v>
@@ -14575,7 +14639,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B115" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
         <x:v>251</x:v>
@@ -14680,7 +14744,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B116" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
         <x:v>253</x:v>
@@ -14785,7 +14849,7 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B117" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
         <x:v>255</x:v>
@@ -14890,7 +14954,7 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="B118" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
         <x:v>257</x:v>
@@ -14995,7 +15059,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B119" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
         <x:v>259</x:v>
@@ -15100,7 +15164,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B120" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
         <x:v>261</x:v>
@@ -15205,7 +15269,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B121" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
         <x:v>263</x:v>
@@ -15310,7 +15374,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B122" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
         <x:v>265</x:v>
@@ -15415,7 +15479,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B123" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
         <x:v>267</x:v>
@@ -15520,7 +15584,7 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B124" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
         <x:v>269</x:v>
@@ -15625,7 +15689,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B125" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
         <x:v>271</x:v>
@@ -15730,7 +15794,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="B126" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
         <x:v>273</x:v>
@@ -15835,7 +15899,7 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B127" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
         <x:v>275</x:v>
@@ -15940,7 +16004,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B128" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
         <x:v>277</x:v>
@@ -16045,7 +16109,7 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B129" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
         <x:v>279</x:v>
@@ -16150,7 +16214,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B130" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
         <x:v>281</x:v>
@@ -16255,7 +16319,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B131" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
         <x:v>283</x:v>
@@ -16574,7 +16638,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B134" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
         <x:v>292</x:v>
@@ -16679,7 +16743,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B135" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
         <x:v>294</x:v>
@@ -16784,7 +16848,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B136" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
         <x:v>296</x:v>
@@ -16889,7 +16953,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B137" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
         <x:v>299</x:v>
@@ -16994,7 +17058,7 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B138" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
         <x:v>301</x:v>
@@ -17099,7 +17163,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B139" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
         <x:v>303</x:v>
@@ -17204,7 +17268,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B140" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
         <x:v>305</x:v>
@@ -17416,7 +17480,7 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B142" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
         <x:v>309</x:v>
@@ -17628,7 +17692,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B144" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
         <x:v>313</x:v>
@@ -17733,7 +17797,7 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B145" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
         <x:v>315</x:v>
@@ -17838,7 +17902,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B146" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
         <x:v>316</x:v>
@@ -18157,7 +18221,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B149" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
         <x:v>323</x:v>
@@ -18262,7 +18326,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B150" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
         <x:v>325</x:v>
@@ -18367,7 +18431,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B151" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
         <x:v>327</x:v>
@@ -18472,7 +18536,7 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B152" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
         <x:v>329</x:v>
@@ -18577,7 +18641,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B153" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
         <x:v>331</x:v>
@@ -18682,7 +18746,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B154" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
         <x:v>333</x:v>
@@ -19001,7 +19065,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B157" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
         <x:v>340</x:v>
@@ -19106,7 +19170,7 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B158" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
         <x:v>342</x:v>
@@ -19211,7 +19275,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B159" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
         <x:v>344</x:v>
@@ -19334,7 +19398,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I160" s="10" t="s">
         <x:v>22</x:v>
@@ -19423,7 +19487,7 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B161" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
         <x:v>348</x:v>
@@ -19441,7 +19505,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I161" s="10" t="s">
         <x:v>22</x:v>
@@ -19528,7 +19592,7 @@
         <x:v>156</x:v>
       </x:c>
       <x:c r="B162" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
         <x:v>350</x:v>
@@ -19633,7 +19697,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B163" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
         <x:v>352</x:v>
@@ -19845,7 +19909,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="B165" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>356</x:v>
@@ -19950,7 +20014,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B166" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
         <x:v>358</x:v>
@@ -20055,7 +20119,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B167" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
         <x:v>360</x:v>
@@ -20160,7 +20224,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="B168" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
         <x:v>362</x:v>
@@ -20265,7 +20329,7 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B169" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
         <x:v>364</x:v>
@@ -20370,7 +20434,7 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B170" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
         <x:v>366</x:v>
@@ -20475,7 +20539,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B171" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
         <x:v>368</x:v>
@@ -20687,7 +20751,7 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B173" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
         <x:v>372</x:v>
@@ -20792,7 +20856,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B174" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
         <x:v>374</x:v>
@@ -21004,7 +21068,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B176" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
         <x:v>378</x:v>
@@ -21109,7 +21173,7 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B177" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
         <x:v>380</x:v>
@@ -21214,7 +21278,7 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B178" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
         <x:v>382</x:v>
@@ -21319,7 +21383,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B179" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
         <x:v>384</x:v>
@@ -21531,7 +21595,7 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B181" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
         <x:v>388</x:v>
@@ -21636,7 +21700,7 @@
         <x:v>176</x:v>
       </x:c>
       <x:c r="B182" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
         <x:v>390</x:v>
@@ -21741,7 +21805,7 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B183" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
         <x:v>392</x:v>
@@ -21846,7 +21910,7 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B184" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
         <x:v>394</x:v>
@@ -21951,7 +22015,7 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B185" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
         <x:v>396</x:v>
@@ -22056,7 +22120,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B186" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
         <x:v>398</x:v>
@@ -22161,7 +22225,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B187" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
         <x:v>400</x:v>
@@ -22266,7 +22330,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B188" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
         <x:v>402</x:v>
@@ -22371,7 +22435,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B189" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
         <x:v>404</x:v>
@@ -22583,7 +22647,7 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B191" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
         <x:v>408</x:v>
@@ -22688,7 +22752,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="B192" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
         <x:v>410</x:v>
@@ -22811,7 +22875,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I193" s="10" t="s">
         <x:v>22</x:v>
@@ -22918,7 +22982,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I194" s="10" t="s">
         <x:v>22</x:v>
@@ -23025,7 +23089,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H195" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I195" s="10" t="s">
         <x:v>22</x:v>
@@ -23129,10 +23193,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G196" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H196" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I196" s="10" t="s">
         <x:v>22</x:v>
@@ -23221,7 +23285,7 @@
         <x:v>191</x:v>
       </x:c>
       <x:c r="B197" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
         <x:v>421</x:v>
@@ -23239,7 +23303,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H197" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I197" s="10" t="s">
         <x:v>22</x:v>
@@ -23326,7 +23390,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="B198" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
         <x:v>423</x:v>
@@ -23341,7 +23405,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G198" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H198" s="1" t="s">
         <x:v>425</x:v>
@@ -23431,7 +23495,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B199" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
         <x:v>426</x:v>
@@ -23446,7 +23510,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G199" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H199" s="1" t="s">
         <x:v>425</x:v>
@@ -23536,7 +23600,7 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="B200" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
         <x:v>428</x:v>
@@ -23551,7 +23615,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G200" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H200" s="1" t="s">
         <x:v>425</x:v>
@@ -23641,7 +23705,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="B201" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
         <x:v>430</x:v>
@@ -23659,7 +23723,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H201" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I201" s="10" t="s">
         <x:v>22</x:v>
@@ -23746,7 +23810,7 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B202" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
         <x:v>432</x:v>
@@ -23764,7 +23828,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H202" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I202" s="10" t="s">
         <x:v>22</x:v>
@@ -23851,7 +23915,7 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="B203" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C203" s="1" t="s">
         <x:v>434</x:v>
@@ -23866,7 +23930,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G203" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H203" s="1" t="s">
         <x:v>436</x:v>
@@ -23956,7 +24020,7 @@
         <x:v>198</x:v>
       </x:c>
       <x:c r="B204" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
         <x:v>437</x:v>
@@ -23974,7 +24038,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H204" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I204" s="10" t="s">
         <x:v>22</x:v>
@@ -24061,7 +24125,7 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B205" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
         <x:v>439</x:v>
@@ -24076,10 +24140,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G205" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H205" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I205" s="10" t="s">
         <x:v>22</x:v>
@@ -24166,7 +24230,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="B206" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
         <x:v>441</x:v>
@@ -24181,7 +24245,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G206" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H206" s="1" t="s">
         <x:v>425</x:v>
@@ -24271,7 +24335,7 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B207" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
         <x:v>443</x:v>
@@ -24289,7 +24353,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H207" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I207" s="10" t="s">
         <x:v>22</x:v>
@@ -24376,7 +24440,7 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B208" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
         <x:v>445</x:v>
@@ -24391,10 +24455,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G208" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H208" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I208" s="10" t="s">
         <x:v>22</x:v>
@@ -24496,7 +24560,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G209" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H209" s="1" t="s">
         <x:v>289</x:v>
@@ -24588,7 +24652,7 @@
         <x:v>204</x:v>
       </x:c>
       <x:c r="B210" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C210" s="1" t="s">
         <x:v>449</x:v>
@@ -24603,10 +24667,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G210" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H210" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I210" s="10" t="s">
         <x:v>22</x:v>
@@ -24693,7 +24757,7 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B211" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C211" s="1" t="s">
         <x:v>451</x:v>
@@ -24708,10 +24772,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G211" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H211" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I211" s="10" t="s">
         <x:v>22</x:v>
@@ -24798,7 +24862,7 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B212" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C212" s="1" t="s">
         <x:v>453</x:v>
@@ -24813,10 +24877,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G212" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H212" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I212" s="10" t="s">
         <x:v>22</x:v>
@@ -24903,7 +24967,7 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B213" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
         <x:v>455</x:v>
@@ -24918,7 +24982,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G213" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H213" s="1" t="s">
         <x:v>457</x:v>
@@ -25008,7 +25072,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B214" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
         <x:v>458</x:v>
@@ -25023,7 +25087,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G214" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H214" s="1" t="s">
         <x:v>425</x:v>
@@ -25128,7 +25192,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G215" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H215" s="1" t="s">
         <x:v>289</x:v>
@@ -25220,7 +25284,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="B216" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C216" s="1" t="s">
         <x:v>462</x:v>
@@ -25238,7 +25302,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H216" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I216" s="10" t="s">
         <x:v>22</x:v>
@@ -25325,7 +25389,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B217" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C217" s="1" t="s">
         <x:v>464</x:v>
@@ -25340,7 +25404,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G217" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H217" s="1" t="s">
         <x:v>48</x:v>
@@ -25430,7 +25494,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B218" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
         <x:v>466</x:v>
@@ -25445,7 +25509,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G218" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H218" s="1" t="s">
         <x:v>48</x:v>
@@ -25535,7 +25599,7 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B219" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C219" s="1" t="s">
         <x:v>468</x:v>
@@ -25553,7 +25617,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H219" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I219" s="10" t="s">
         <x:v>22</x:v>
@@ -25658,7 +25722,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H220" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I220" s="10" t="s">
         <x:v>22</x:v>
@@ -25762,7 +25826,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G221" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H221" s="1" t="s">
         <x:v>298</x:v>
@@ -25854,7 +25918,7 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="B222" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C222" s="1" t="s">
         <x:v>474</x:v>
@@ -25869,10 +25933,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G222" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H222" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I222" s="10" t="s">
         <x:v>22</x:v>
@@ -25959,7 +26023,7 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B223" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C223" s="1" t="s">
         <x:v>476</x:v>
@@ -25974,10 +26038,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G223" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H223" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I223" s="10" t="s">
         <x:v>22</x:v>
@@ -26064,7 +26128,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="B224" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C224" s="1" t="s">
         <x:v>478</x:v>
@@ -26079,7 +26143,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G224" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H224" s="1" t="s">
         <x:v>335</x:v>
@@ -26169,7 +26233,7 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="B225" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C225" s="1" t="s">
         <x:v>480</x:v>
@@ -26184,7 +26248,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G225" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H225" s="1" t="s">
         <x:v>335</x:v>
@@ -26274,7 +26338,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B226" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C226" s="1" t="s">
         <x:v>482</x:v>
@@ -26289,7 +26353,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G226" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H226" s="1" t="s">
         <x:v>335</x:v>
@@ -26379,7 +26443,7 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B227" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C227" s="1" t="s">
         <x:v>484</x:v>
@@ -26394,7 +26458,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G227" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H227" s="1" t="s">
         <x:v>335</x:v>
@@ -26484,7 +26548,7 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B228" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C228" s="1" t="s">
         <x:v>486</x:v>
@@ -26499,7 +26563,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G228" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H228" s="1" t="s">
         <x:v>335</x:v>
@@ -26589,7 +26653,7 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B229" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C229" s="1" t="s">
         <x:v>488</x:v>
@@ -26604,7 +26668,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G229" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H229" s="1" t="s">
         <x:v>335</x:v>
@@ -26694,7 +26758,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B230" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C230" s="1" t="s">
         <x:v>490</x:v>
@@ -26799,7 +26863,7 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="B231" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C231" s="1" t="s">
         <x:v>492</x:v>
@@ -26814,10 +26878,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G231" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H231" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I231" s="10" t="s">
         <x:v>22</x:v>
@@ -26904,7 +26968,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B232" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C232" s="1" t="s">
         <x:v>494</x:v>
@@ -27009,7 +27073,7 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="B233" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C233" s="1" t="s">
         <x:v>496</x:v>
@@ -27024,7 +27088,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G233" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H233" s="1" t="s">
         <x:v>286</x:v>
@@ -27114,7 +27178,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="B234" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C234" s="1" t="s">
         <x:v>498</x:v>
@@ -27129,7 +27193,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G234" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H234" s="1" t="s">
         <x:v>457</x:v>
@@ -27219,7 +27283,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B235" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C235" s="1" t="s">
         <x:v>500</x:v>
@@ -27234,10 +27298,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G235" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H235" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I235" s="10" t="s">
         <x:v>22</x:v>
@@ -27324,7 +27388,7 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B236" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C236" s="1" t="s">
         <x:v>502</x:v>
@@ -27339,10 +27403,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G236" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H236" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I236" s="10" t="s">
         <x:v>22</x:v>
@@ -27429,7 +27493,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="B237" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C237" s="1" t="s">
         <x:v>505</x:v>
@@ -27444,7 +27508,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G237" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H237" s="1" t="s">
         <x:v>28</x:v>
@@ -27549,10 +27613,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G238" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H238" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I238" s="10" t="s">
         <x:v>22</x:v>
@@ -27641,7 +27705,7 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B239" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C239" s="1" t="s">
         <x:v>509</x:v>
@@ -27656,7 +27720,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G239" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H239" s="1" t="s">
         <x:v>25</x:v>
@@ -27746,7 +27810,7 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="B240" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C240" s="1" t="s">
         <x:v>511</x:v>
@@ -27761,7 +27825,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G240" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H240" s="1" t="s">
         <x:v>425</x:v>
@@ -27851,7 +27915,7 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B241" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C241" s="1" t="s">
         <x:v>513</x:v>
@@ -27866,7 +27930,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G241" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H241" s="1" t="s">
         <x:v>515</x:v>
@@ -27956,7 +28020,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B242" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C242" s="1" t="s">
         <x:v>516</x:v>
@@ -27971,7 +28035,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G242" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H242" s="1" t="s">
         <x:v>515</x:v>
@@ -28061,7 +28125,7 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B243" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C243" s="1" t="s">
         <x:v>518</x:v>
@@ -28076,7 +28140,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G243" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H243" s="1" t="s">
         <x:v>425</x:v>
@@ -28166,7 +28230,7 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B244" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C244" s="1" t="s">
         <x:v>520</x:v>
@@ -28181,7 +28245,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G244" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H244" s="1" t="s">
         <x:v>425</x:v>
@@ -28286,7 +28350,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G245" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H245" s="1" t="s">
         <x:v>298</x:v>
@@ -28393,7 +28457,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G246" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H246" s="1" t="s">
         <x:v>298</x:v>
@@ -28485,7 +28549,7 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B247" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C247" s="1" t="s">
         <x:v>526</x:v>
@@ -28500,7 +28564,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G247" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H247" s="1" t="s">
         <x:v>436</x:v>
@@ -28590,7 +28654,7 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B248" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C248" s="1" t="s">
         <x:v>529</x:v>
@@ -28605,7 +28669,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G248" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H248" s="1" t="s">
         <x:v>436</x:v>
@@ -28695,7 +28759,7 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B249" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C249" s="1" t="s">
         <x:v>531</x:v>
@@ -28710,10 +28774,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G249" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H249" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I249" s="10" t="s">
         <x:v>22</x:v>
@@ -28815,7 +28879,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G250" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H250" s="1" t="s">
         <x:v>535</x:v>
@@ -28922,7 +28986,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G251" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H251" s="1" t="s">
         <x:v>335</x:v>
@@ -29014,7 +29078,7 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="B252" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C252" s="1" t="s">
         <x:v>538</x:v>
@@ -29029,10 +29093,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G252" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H252" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I252" s="10" t="s">
         <x:v>22</x:v>
@@ -29119,7 +29183,7 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="B253" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C253" s="1" t="s">
         <x:v>540</x:v>
@@ -29134,7 +29198,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G253" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H253" s="1" t="s">
         <x:v>436</x:v>
@@ -29224,7 +29288,7 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="B254" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C254" s="1" t="s">
         <x:v>542</x:v>
@@ -29239,7 +29303,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G254" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H254" s="1" t="s">
         <x:v>436</x:v>
@@ -29329,7 +29393,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B255" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C255" s="1" t="s">
         <x:v>544</x:v>
@@ -29344,7 +29408,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G255" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H255" s="1" t="s">
         <x:v>425</x:v>
@@ -29434,7 +29498,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="B256" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C256" s="1" t="s">
         <x:v>546</x:v>
@@ -29449,10 +29513,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G256" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H256" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I256" s="10" t="s">
         <x:v>22</x:v>
@@ -29539,7 +29603,7 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="B257" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C257" s="1" t="s">
         <x:v>548</x:v>
@@ -29554,7 +29618,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G257" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H257" s="1" t="s">
         <x:v>436</x:v>
@@ -29644,7 +29708,7 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B258" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C258" s="1" t="s">
         <x:v>550</x:v>
@@ -29659,7 +29723,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G258" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H258" s="1" t="s">
         <x:v>335</x:v>
@@ -29764,7 +29828,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G259" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H259" s="1" t="s">
         <x:v>335</x:v>
@@ -29856,7 +29920,7 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="B260" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C260" s="1" t="s">
         <x:v>554</x:v>
@@ -29871,7 +29935,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G260" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H260" s="1" t="s">
         <x:v>48</x:v>
@@ -29961,7 +30025,7 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B261" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C261" s="1" t="s">
         <x:v>556</x:v>
@@ -29976,7 +30040,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G261" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H261" s="1" t="s">
         <x:v>425</x:v>
@@ -30081,7 +30145,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G262" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H262" s="1" t="s">
         <x:v>535</x:v>
@@ -30173,7 +30237,7 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="B263" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C263" s="1" t="s">
         <x:v>561</x:v>
@@ -30188,7 +30252,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G263" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H263" s="1" t="s">
         <x:v>21</x:v>
@@ -30278,7 +30342,7 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B264" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C264" s="1" t="s">
         <x:v>563</x:v>
@@ -30293,7 +30357,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G264" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H264" s="1" t="s">
         <x:v>21</x:v>
@@ -30383,7 +30447,7 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B265" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C265" s="1" t="s">
         <x:v>565</x:v>
@@ -30398,7 +30462,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G265" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H265" s="1" t="s">
         <x:v>457</x:v>
@@ -30488,7 +30552,7 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="B266" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C266" s="1" t="s">
         <x:v>567</x:v>
@@ -30503,10 +30567,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G266" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H266" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I266" s="10" t="s">
         <x:v>22</x:v>
@@ -30593,7 +30657,7 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B267" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C267" s="1" t="s">
         <x:v>569</x:v>
@@ -30608,7 +30672,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G267" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H267" s="1" t="s">
         <x:v>28</x:v>
@@ -30698,7 +30762,7 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B268" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C268" s="1" t="s">
         <x:v>571</x:v>
@@ -30713,7 +30777,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G268" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H268" s="1" t="s">
         <x:v>515</x:v>
@@ -30803,7 +30867,7 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B269" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C269" s="1" t="s">
         <x:v>573</x:v>
@@ -30821,7 +30885,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H269" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I269" s="10" t="s">
         <x:v>22</x:v>
@@ -30908,7 +30972,7 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B270" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C270" s="1" t="s">
         <x:v>576</x:v>
@@ -31013,7 +31077,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B271" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C271" s="1" t="s">
         <x:v>578</x:v>
@@ -31031,7 +31095,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H271" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I271" s="10" t="s">
         <x:v>22</x:v>
@@ -31118,7 +31182,7 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="B272" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C272" s="1" t="s">
         <x:v>580</x:v>
@@ -31133,10 +31197,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G272" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H272" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I272" s="10" t="s">
         <x:v>22</x:v>
@@ -31223,7 +31287,7 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B273" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C273" s="1" t="s">
         <x:v>582</x:v>
@@ -31241,7 +31305,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H273" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I273" s="10" t="s">
         <x:v>22</x:v>
@@ -31328,7 +31392,7 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="B274" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C274" s="1" t="s">
         <x:v>584</x:v>
@@ -31343,10 +31407,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G274" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H274" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I274" s="10" t="s">
         <x:v>22</x:v>
@@ -31433,7 +31497,7 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="B275" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C275" s="1" t="s">
         <x:v>586</x:v>
@@ -31448,10 +31512,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G275" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H275" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I275" s="10" t="s">
         <x:v>22</x:v>
@@ -31538,7 +31602,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B276" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C276" s="1" t="s">
         <x:v>588</x:v>
@@ -31643,7 +31707,7 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="B277" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C277" s="1" t="s">
         <x:v>590</x:v>
@@ -31658,10 +31722,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G277" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H277" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I277" s="10" t="s">
         <x:v>22</x:v>
@@ -31748,7 +31812,7 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="B278" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C278" s="1" t="s">
         <x:v>592</x:v>
@@ -31763,7 +31827,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G278" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H278" s="1" t="s">
         <x:v>457</x:v>
@@ -31853,7 +31917,7 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B279" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C279" s="1" t="s">
         <x:v>594</x:v>
@@ -31868,7 +31932,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G279" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H279" s="1" t="s">
         <x:v>289</x:v>
@@ -31958,7 +32022,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="B280" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C280" s="1" t="s">
         <x:v>596</x:v>
@@ -31973,7 +32037,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G280" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H280" s="1" t="s">
         <x:v>335</x:v>
@@ -32063,7 +32127,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B281" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C281" s="1" t="s">
         <x:v>598</x:v>
@@ -32168,7 +32232,7 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B282" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C282" s="1" t="s">
         <x:v>601</x:v>
@@ -32186,7 +32250,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H282" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I282" s="10" t="s">
         <x:v>22</x:v>
@@ -32273,7 +32337,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B283" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C283" s="1" t="s">
         <x:v>603</x:v>
@@ -32291,7 +32355,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H283" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I283" s="10" t="s">
         <x:v>22</x:v>
@@ -32378,7 +32442,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="B284" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C284" s="1" t="s">
         <x:v>605</x:v>
@@ -32483,7 +32547,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B285" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C285" s="1" t="s">
         <x:v>607</x:v>
@@ -32588,7 +32652,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="B286" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C286" s="1" t="s">
         <x:v>609</x:v>
@@ -32693,7 +32757,7 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="B287" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C287" s="1" t="s">
         <x:v>611</x:v>
@@ -32711,7 +32775,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H287" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I287" s="10" t="s">
         <x:v>22</x:v>
@@ -32798,7 +32862,7 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="B288" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C288" s="1" t="s">
         <x:v>613</x:v>
@@ -32903,7 +32967,7 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="B289" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C289" s="1" t="s">
         <x:v>615</x:v>
@@ -32921,7 +32985,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H289" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I289" s="10" t="s">
         <x:v>22</x:v>
@@ -33008,7 +33072,7 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="B290" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C290" s="1" t="s">
         <x:v>617</x:v>
@@ -33113,7 +33177,7 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="B291" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C291" s="1" t="s">
         <x:v>619</x:v>
@@ -33131,7 +33195,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H291" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I291" s="10" t="s">
         <x:v>22</x:v>
@@ -33218,7 +33282,7 @@
         <x:v>286</x:v>
       </x:c>
       <x:c r="B292" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C292" s="1" t="s">
         <x:v>621</x:v>
@@ -33323,7 +33387,7 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="B293" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C293" s="1" t="s">
         <x:v>623</x:v>
@@ -33341,7 +33405,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="H293" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I293" s="10" t="s">
         <x:v>22</x:v>
@@ -33428,7 +33492,7 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B294" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C294" s="1" t="s">
         <x:v>625</x:v>
@@ -33533,7 +33597,7 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="B295" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C295" s="1" t="s">
         <x:v>627</x:v>
@@ -33638,7 +33702,7 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="B296" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C296" s="1" t="s">
         <x:v>629</x:v>
@@ -33743,7 +33807,7 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B297" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C297" s="1" t="s">
         <x:v>631</x:v>
@@ -33848,7 +33912,7 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="B298" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C298" s="1" t="s">
         <x:v>633</x:v>
@@ -33953,7 +34017,7 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="B299" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C299" s="1" t="s">
         <x:v>635</x:v>
@@ -34058,7 +34122,7 @@
         <x:v>294</x:v>
       </x:c>
       <x:c r="B300" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C300" s="1" t="s">
         <x:v>637</x:v>
@@ -34163,7 +34227,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="B301" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C301" s="1" t="s">
         <x:v>639</x:v>
@@ -34268,7 +34332,7 @@
         <x:v>296</x:v>
       </x:c>
       <x:c r="B302" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C302" s="1" t="s">
         <x:v>641</x:v>
@@ -34373,7 +34437,7 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="B303" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C303" s="1" t="s">
         <x:v>643</x:v>
@@ -34478,7 +34542,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B304" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C304" s="1" t="s">
         <x:v>645</x:v>
@@ -34493,7 +34557,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G304" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H304" s="1" t="s">
         <x:v>102</x:v>
@@ -34583,7 +34647,7 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B305" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C305" s="1" t="s">
         <x:v>648</x:v>
@@ -34598,7 +34662,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G305" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H305" s="1" t="s">
         <x:v>102</x:v>
@@ -34688,7 +34752,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="B306" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C306" s="1" t="s">
         <x:v>650</x:v>
@@ -34703,7 +34767,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G306" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H306" s="1" t="s">
         <x:v>102</x:v>
@@ -34793,7 +34857,7 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B307" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C307" s="1" t="s">
         <x:v>652</x:v>
@@ -34808,7 +34872,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G307" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H307" s="1" t="s">
         <x:v>102</x:v>
@@ -34898,7 +34962,7 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="B308" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C308" s="1" t="s">
         <x:v>654</x:v>
@@ -34913,7 +34977,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G308" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H308" s="1" t="s">
         <x:v>102</x:v>
@@ -35003,7 +35067,7 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="B309" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C309" s="1" t="s">
         <x:v>656</x:v>
@@ -35018,7 +35082,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G309" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H309" s="1" t="s">
         <x:v>102</x:v>
@@ -35108,7 +35172,7 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B310" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C310" s="1" t="s">
         <x:v>658</x:v>
@@ -35123,7 +35187,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G310" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H310" s="1" t="s">
         <x:v>102</x:v>
@@ -35213,7 +35277,7 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="B311" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C311" s="1" t="s">
         <x:v>660</x:v>
@@ -35228,7 +35292,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G311" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H311" s="1" t="s">
         <x:v>102</x:v>
@@ -35318,7 +35382,7 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="B312" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C312" s="1" t="s">
         <x:v>662</x:v>
@@ -35333,7 +35397,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G312" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H312" s="1" t="s">
         <x:v>102</x:v>
@@ -35423,7 +35487,7 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B313" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C313" s="1" t="s">
         <x:v>664</x:v>
@@ -35438,7 +35502,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G313" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H313" s="1" t="s">
         <x:v>102</x:v>
@@ -35528,7 +35592,7 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="B314" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C314" s="1" t="s">
         <x:v>666</x:v>
@@ -35543,7 +35607,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G314" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H314" s="1" t="s">
         <x:v>102</x:v>
@@ -35633,7 +35697,7 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="B315" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C315" s="1" t="s">
         <x:v>668</x:v>
@@ -35648,7 +35712,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G315" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H315" s="1" t="s">
         <x:v>102</x:v>
@@ -35738,7 +35802,7 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B316" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C316" s="1" t="s">
         <x:v>670</x:v>
@@ -35753,7 +35817,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G316" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H316" s="1" t="s">
         <x:v>102</x:v>
@@ -35843,7 +35907,7 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B317" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C317" s="1" t="s">
         <x:v>672</x:v>
@@ -35858,7 +35922,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G317" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H317" s="1" t="s">
         <x:v>102</x:v>
@@ -35948,7 +36012,7 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="B318" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C318" s="1" t="s">
         <x:v>674</x:v>
@@ -35963,7 +36027,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G318" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H318" s="1" t="s">
         <x:v>102</x:v>
@@ -36053,7 +36117,7 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="B319" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C319" s="1" t="s">
         <x:v>676</x:v>
@@ -36065,10 +36129,10 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="F319" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G319" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H319" s="1" t="s">
         <x:v>102</x:v>
@@ -36158,7 +36222,7 @@
         <x:v>314</x:v>
       </x:c>
       <x:c r="B320" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C320" s="1" t="s">
         <x:v>679</x:v>
@@ -36170,10 +36234,10 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="F320" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G320" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H320" s="1" t="s">
         <x:v>102</x:v>
@@ -36263,7 +36327,7 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="B321" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C321" s="1" t="s">
         <x:v>680</x:v>
@@ -36275,10 +36339,10 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="F321" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G321" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H321" s="1" t="s">
         <x:v>102</x:v>
@@ -36368,7 +36432,7 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="B322" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C322" s="1" t="s">
         <x:v>682</x:v>
@@ -36380,10 +36444,10 @@
         <x:v>678</x:v>
       </x:c>
       <x:c r="F322" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G322" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H322" s="1" t="s">
         <x:v>102</x:v>
@@ -36473,7 +36537,7 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B323" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C323" s="1" t="s">
         <x:v>684</x:v>
@@ -36488,7 +36552,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G323" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H323" s="1" t="s">
         <x:v>102</x:v>
@@ -36578,7 +36642,7 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="B324" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C324" s="1" t="s">
         <x:v>687</x:v>
@@ -36593,7 +36657,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G324" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H324" s="1" t="s">
         <x:v>102</x:v>
@@ -36683,7 +36747,7 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B325" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C325" s="1" t="s">
         <x:v>688</x:v>
@@ -36698,7 +36762,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G325" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H325" s="1" t="s">
         <x:v>102</x:v>
@@ -36788,7 +36852,7 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="B326" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C326" s="1" t="s">
         <x:v>690</x:v>
@@ -36803,7 +36867,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G326" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H326" s="1" t="s">
         <x:v>102</x:v>
@@ -36893,7 +36957,7 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B327" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C327" s="1" t="s">
         <x:v>692</x:v>
@@ -36908,7 +36972,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G327" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H327" s="1" t="s">
         <x:v>102</x:v>
@@ -36998,7 +37062,7 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="B328" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C328" s="1" t="s">
         <x:v>694</x:v>
@@ -37013,7 +37077,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G328" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H328" s="1" t="s">
         <x:v>102</x:v>
@@ -37103,7 +37167,7 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B329" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C329" s="1" t="s">
         <x:v>695</x:v>
@@ -37118,7 +37182,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G329" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H329" s="1" t="s">
         <x:v>102</x:v>
@@ -37208,7 +37272,7 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="B330" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C330" s="1" t="s">
         <x:v>697</x:v>
@@ -37223,7 +37287,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G330" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H330" s="1" t="s">
         <x:v>102</x:v>
@@ -37313,7 +37377,7 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="B331" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C331" s="1" t="s">
         <x:v>698</x:v>
@@ -37328,7 +37392,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G331" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H331" s="1" t="s">
         <x:v>102</x:v>
@@ -37418,7 +37482,7 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="B332" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C332" s="1" t="s">
         <x:v>700</x:v>
@@ -37433,7 +37497,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G332" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H332" s="1" t="s">
         <x:v>102</x:v>
@@ -37523,7 +37587,7 @@
         <x:v>327</x:v>
       </x:c>
       <x:c r="B333" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C333" s="1" t="s">
         <x:v>702</x:v>
@@ -37538,7 +37602,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G333" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H333" s="1" t="s">
         <x:v>102</x:v>
@@ -37628,7 +37692,7 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="B334" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C334" s="1" t="s">
         <x:v>704</x:v>
@@ -37643,7 +37707,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G334" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H334" s="1" t="s">
         <x:v>102</x:v>
@@ -37733,7 +37797,7 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="B335" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C335" s="1" t="s">
         <x:v>705</x:v>
@@ -37748,7 +37812,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G335" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H335" s="1" t="s">
         <x:v>102</x:v>
@@ -37838,7 +37902,7 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="B336" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C336" s="1" t="s">
         <x:v>707</x:v>
@@ -37853,7 +37917,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G336" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H336" s="1" t="s">
         <x:v>102</x:v>
@@ -37943,7 +38007,7 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="B337" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C337" s="1" t="s">
         <x:v>709</x:v>
@@ -37958,7 +38022,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G337" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H337" s="1" t="s">
         <x:v>102</x:v>
@@ -38048,7 +38112,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="B338" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C338" s="1" t="s">
         <x:v>711</x:v>
@@ -38060,10 +38124,10 @@
         <x:v>686</x:v>
       </x:c>
       <x:c r="F338" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G338" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H338" s="1" t="s">
         <x:v>102</x:v>
@@ -38153,7 +38217,7 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="B339" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C339" s="1" t="s">
         <x:v>713</x:v>
@@ -38168,7 +38232,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G339" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H339" s="1" t="s">
         <x:v>102</x:v>
@@ -38258,7 +38322,7 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="B340" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C340" s="1" t="s">
         <x:v>715</x:v>
@@ -38273,7 +38337,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G340" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H340" s="1" t="s">
         <x:v>102</x:v>
@@ -38363,7 +38427,7 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="B341" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C341" s="1" t="s">
         <x:v>717</x:v>
@@ -38378,7 +38442,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G341" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H341" s="1" t="s">
         <x:v>102</x:v>
@@ -38468,7 +38532,7 @@
         <x:v>336</x:v>
       </x:c>
       <x:c r="B342" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C342" s="1" t="s">
         <x:v>719</x:v>
@@ -38483,7 +38547,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G342" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H342" s="1" t="s">
         <x:v>102</x:v>
@@ -38573,7 +38637,7 @@
         <x:v>337</x:v>
       </x:c>
       <x:c r="B343" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C343" s="1" t="s">
         <x:v>721</x:v>
@@ -38678,7 +38742,7 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B344" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C344" s="1" t="s">
         <x:v>724</x:v>
@@ -38783,7 +38847,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="B345" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C345" s="1" t="s">
         <x:v>726</x:v>
@@ -38888,7 +38952,7 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="B346" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C346" s="1" t="s">
         <x:v>728</x:v>
@@ -38993,7 +39057,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B347" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C347" s="1" t="s">
         <x:v>729</x:v>
@@ -39098,7 +39162,7 @@
         <x:v>342</x:v>
       </x:c>
       <x:c r="B348" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C348" s="1" t="s">
         <x:v>731</x:v>
@@ -39203,7 +39267,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B349" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C349" s="1" t="s">
         <x:v>733</x:v>
@@ -39308,7 +39372,7 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B350" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C350" s="1" t="s">
         <x:v>735</x:v>
@@ -39320,10 +39384,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F350" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G350" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H350" s="1" t="s">
         <x:v>738</x:v>
@@ -39413,7 +39477,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="B351" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C351" s="1" t="s">
         <x:v>739</x:v>
@@ -39425,13 +39489,13 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F351" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G351" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H351" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I351" s="10" t="s">
         <x:v>741</x:v>
@@ -39518,7 +39582,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="B352" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C352" s="1" t="s">
         <x:v>742</x:v>
@@ -39530,10 +39594,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F352" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G352" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H352" s="1" t="s">
         <x:v>738</x:v>
@@ -39623,7 +39687,7 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="B353" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C353" s="1" t="s">
         <x:v>744</x:v>
@@ -39635,13 +39699,13 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F353" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G353" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H353" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I353" s="10" t="s">
         <x:v>741</x:v>
@@ -39728,7 +39792,7 @@
         <x:v>348</x:v>
       </x:c>
       <x:c r="B354" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
         <x:v>746</x:v>
@@ -39740,10 +39804,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F354" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G354" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H354" s="1" t="s">
         <x:v>748</x:v>
@@ -39833,7 +39897,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="B355" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
         <x:v>749</x:v>
@@ -39845,13 +39909,13 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F355" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G355" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H355" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I355" s="10" t="s">
         <x:v>741</x:v>
@@ -39938,7 +40002,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="B356" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
         <x:v>751</x:v>
@@ -39953,7 +40017,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="G356" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H356" s="1" t="s">
         <x:v>738</x:v>
@@ -40043,7 +40107,7 @@
         <x:v>351</x:v>
       </x:c>
       <x:c r="B357" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
         <x:v>753</x:v>
@@ -40058,7 +40122,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="G357" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H357" s="1" t="s">
         <x:v>289</x:v>
@@ -40148,7 +40212,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="B358" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C358" s="1" t="s">
         <x:v>755</x:v>
@@ -40160,10 +40224,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F358" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G358" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H358" s="1" t="s">
         <x:v>738</x:v>
@@ -40253,7 +40317,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="B359" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C359" s="1" t="s">
         <x:v>757</x:v>
@@ -40265,10 +40329,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F359" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G359" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H359" s="1" t="s">
         <x:v>738</x:v>
@@ -40358,7 +40422,7 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="B360" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C360" s="1" t="s">
         <x:v>759</x:v>
@@ -40370,13 +40434,13 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F360" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G360" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H360" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I360" s="10" t="s">
         <x:v>741</x:v>
@@ -40463,7 +40527,7 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="B361" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
         <x:v>761</x:v>
@@ -40475,13 +40539,13 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F361" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G361" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H361" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I361" s="10" t="s">
         <x:v>741</x:v>
@@ -40568,7 +40632,7 @@
         <x:v>356</x:v>
       </x:c>
       <x:c r="B362" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
         <x:v>763</x:v>
@@ -40580,10 +40644,10 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F362" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G362" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H362" s="1" t="s">
         <x:v>748</x:v>
@@ -40673,7 +40737,7 @@
         <x:v>357</x:v>
       </x:c>
       <x:c r="B363" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C363" s="1" t="s">
         <x:v>765</x:v>
@@ -40685,13 +40749,13 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F363" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G363" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H363" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I363" s="10" t="s">
         <x:v>741</x:v>
@@ -40778,7 +40842,7 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="B364" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C364" s="1" t="s">
         <x:v>767</x:v>
@@ -40790,13 +40854,13 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F364" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G364" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H364" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I364" s="10" t="s">
         <x:v>741</x:v>
@@ -40883,7 +40947,7 @@
         <x:v>359</x:v>
       </x:c>
       <x:c r="B365" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C365" s="1" t="s">
         <x:v>769</x:v>
@@ -40898,7 +40962,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="G365" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H365" s="1" t="s">
         <x:v>773</x:v>
@@ -40988,7 +41052,7 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="B366" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C366" s="1" t="s">
         <x:v>774</x:v>
@@ -41003,7 +41067,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="G366" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H366" s="1" t="s">
         <x:v>773</x:v>
@@ -41093,7 +41157,7 @@
         <x:v>361</x:v>
       </x:c>
       <x:c r="B367" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C367" s="1" t="s">
         <x:v>775</x:v>
@@ -41108,7 +41172,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="G367" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H367" s="1" t="s">
         <x:v>773</x:v>
@@ -41198,7 +41262,7 @@
         <x:v>362</x:v>
       </x:c>
       <x:c r="B368" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C368" s="1" t="s">
         <x:v>777</x:v>
@@ -41213,7 +41277,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="G368" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H368" s="1" t="s">
         <x:v>773</x:v>
@@ -41303,7 +41367,7 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="B369" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C369" s="1" t="s">
         <x:v>778</x:v>
@@ -41318,7 +41382,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="G369" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H369" s="1" t="s">
         <x:v>773</x:v>
@@ -41408,7 +41472,7 @@
         <x:v>364</x:v>
       </x:c>
       <x:c r="B370" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C370" s="1" t="s">
         <x:v>779</x:v>
@@ -41423,7 +41487,7 @@
         <x:v>772</x:v>
       </x:c>
       <x:c r="G370" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H370" s="1" t="s">
         <x:v>782</x:v>
@@ -41513,7 +41577,7 @@
         <x:v>365</x:v>
       </x:c>
       <x:c r="B371" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C371" s="1" t="s">
         <x:v>783</x:v>
@@ -41528,7 +41592,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G371" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H371" s="1" t="s">
         <x:v>786</x:v>
@@ -41618,7 +41682,7 @@
         <x:v>366</x:v>
       </x:c>
       <x:c r="B372" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C372" s="1" t="s">
         <x:v>787</x:v>
@@ -41633,7 +41697,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G372" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H372" s="1" t="s">
         <x:v>786</x:v>
@@ -41723,7 +41787,7 @@
         <x:v>367</x:v>
       </x:c>
       <x:c r="B373" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C373" s="1" t="s">
         <x:v>789</x:v>
@@ -41738,7 +41802,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G373" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H373" s="1" t="s">
         <x:v>786</x:v>
@@ -41828,7 +41892,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B374" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C374" s="1" t="s">
         <x:v>791</x:v>
@@ -41843,7 +41907,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G374" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H374" s="1" t="s">
         <x:v>786</x:v>
@@ -41933,7 +41997,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="B375" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C375" s="1" t="s">
         <x:v>793</x:v>
@@ -41948,7 +42012,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G375" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H375" s="1" t="s">
         <x:v>786</x:v>
@@ -42038,7 +42102,7 @@
         <x:v>370</x:v>
       </x:c>
       <x:c r="B376" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C376" s="1" t="s">
         <x:v>795</x:v>
@@ -42053,7 +42117,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G376" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H376" s="1" t="s">
         <x:v>786</x:v>
@@ -42143,7 +42207,7 @@
         <x:v>371</x:v>
       </x:c>
       <x:c r="B377" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C377" s="1" t="s">
         <x:v>797</x:v>
@@ -42155,13 +42219,13 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="F377" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G377" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H377" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I377" s="10" t="s">
         <x:v>741</x:v>
@@ -42248,7 +42312,7 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="B378" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C378" s="1" t="s">
         <x:v>800</x:v>
@@ -42260,13 +42324,13 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="F378" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G378" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H378" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I378" s="10" t="s">
         <x:v>741</x:v>
@@ -42353,7 +42417,7 @@
         <x:v>373</x:v>
       </x:c>
       <x:c r="B379" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C379" s="1" t="s">
         <x:v>802</x:v>
@@ -42365,13 +42429,13 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="F379" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G379" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H379" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I379" s="10" t="s">
         <x:v>741</x:v>
@@ -42458,7 +42522,7 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="B380" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C380" s="1" t="s">
         <x:v>804</x:v>
@@ -42563,7 +42627,7 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B381" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C381" s="1" t="s">
         <x:v>807</x:v>
@@ -42575,13 +42639,13 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="F381" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="G381" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H381" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="I381" s="10" t="s">
         <x:v>741</x:v>
@@ -42686,7 +42750,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R596cd1e0efd8487c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4579a698538345c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/GaelGunStore_B42_checklist.xlsx
+++ b/docs/GaelGunStore_B42_checklist.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armas" sheetId="1" r:id="R44a274d89f604d52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armas" sheetId="1" r:id="R080a24d87d9d43e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -574,112 +574,112 @@
     <x:t xml:space="preserve">Webley_Revolver 38</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Base.AEK919</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">AEK919 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Subfusiles de una mano</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Auto</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Auto/Single</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.CBJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">CBJ 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.MAC10</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MAC10 .45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Micro_UZI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Micro_UZI 22LR</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.MP7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MP7 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.MP9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MP9 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.MSST</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">MSST 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.P90</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">P90 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.P99_Kilin</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">P99_Kilin 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.PP2000</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PP2000 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.PP93</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PP93 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.TEC9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TEC9 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.TMP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">TMP 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.UZI</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">UZI 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.Veresk</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Veresk 9mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Base.VZ61</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">VZ61 22LR</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">☐</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.AEK919</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">AEK919 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Subfusiles de una mano</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Auto</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Auto/Single</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.CBJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CBJ 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.MAC10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MAC10 .45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Micro_UZI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Micro_UZI 22LR</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.MP7</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MP7 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.MP9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MP9 45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.MSST</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">MSST 45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.P90</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">P90 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.P99_Kilin</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">P99_Kilin 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.PP2000</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PP2000 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.PP93</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PP93 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.TEC9</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TEC9 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.TMP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">TMP 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.UZI</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">UZI 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.Veresk</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Veresk 9mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Base.VZ61</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">VZ61 22LR</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Base.A2000</x:t>
@@ -2985,7 +2985,7 @@
       </x:c>
       <x:c r="E3" s="5" t="n">
         <x:f>COUNTIF(B7:B381,"☑")+COUNTIF(B7:B381,"Hecho/Automatizado")</x:f>
-        <x:v>107</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="F3" s="1"/>
       <x:c r="G3" s="4" t="s">
@@ -2993,7 +2993,7 @@
       </x:c>
       <x:c r="H3" s="5" t="n">
         <x:f>B3-E3</x:f>
-        <x:v>268</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="I3" s="1"/>
       <x:c r="J3" s="1"/>
@@ -8384,7 +8384,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B56" s="11" t="str">
-        <x:v>☐</x:v>
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>127</x:v>
@@ -8408,7 +8408,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="J56" s="1" t="str">
-        <x:v>Sin perfil ADS personal guardado</x:v>
+        <x:v>Mira de hierro calibrada manualmente</x:v>
       </x:c>
       <x:c r="K56" s="24" t="str">
         <x:v>No aplica</x:v>
@@ -11593,23 +11593,23 @@
       <x:c r="A86" s="9">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B86" s="11" t="s">
+      <x:c r="B86" s="11" t="str">
+        <x:v>☑</x:v>
+      </x:c>
+      <x:c r="C86" s="1" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="C86" s="1" t="s">
+      <x:c r="D86" s="1" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="D86" s="1" t="s">
+      <x:c r="E86" s="13" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="E86" s="13" t="s">
+      <x:c r="F86" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F86" s="1" t="s">
+      <x:c r="G86" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G86" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H86" s="1" t="s">
         <x:v>31</x:v>
@@ -11617,7 +11617,9 @@
       <x:c r="I86" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J86" s="1"/>
+      <x:c r="J86" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K86" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -11698,23 +11700,23 @@
       <x:c r="A87" s="9">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="B87" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B87" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D87" s="1" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="D87" s="1" t="s">
-        <x:v>195</x:v>
-      </x:c>
       <x:c r="E87" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F87" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F87" s="1" t="s">
+      <x:c r="G87" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G87" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H87" s="1" t="s">
         <x:v>31</x:v>
@@ -11722,7 +11724,9 @@
       <x:c r="I87" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J87" s="1"/>
+      <x:c r="J87" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K87" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -11803,23 +11807,23 @@
       <x:c r="A88" s="9">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B88" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B88" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D88" s="1" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="D88" s="1" t="s">
-        <x:v>197</x:v>
-      </x:c>
       <x:c r="E88" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F88" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F88" s="1" t="s">
+      <x:c r="G88" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G88" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H88" s="1" t="s">
         <x:v>51</x:v>
@@ -11827,7 +11831,9 @@
       <x:c r="I88" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J88" s="1"/>
+      <x:c r="J88" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K88" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -11908,23 +11914,23 @@
       <x:c r="A89" s="9">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="B89" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B89" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="D89" s="1" t="s">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="D89" s="1" t="s">
-        <x:v>199</x:v>
-      </x:c>
       <x:c r="E89" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F89" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F89" s="1" t="s">
+      <x:c r="G89" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G89" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H89" s="1" t="s">
         <x:v>48</x:v>
@@ -11932,7 +11938,9 @@
       <x:c r="I89" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J89" s="1"/>
+      <x:c r="J89" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K89" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12013,23 +12021,23 @@
       <x:c r="A90" s="9">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="B90" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B90" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D90" s="1" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="D90" s="1" t="s">
-        <x:v>201</x:v>
-      </x:c>
       <x:c r="E90" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F90" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F90" s="1" t="s">
+      <x:c r="G90" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G90" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H90" s="1" t="s">
         <x:v>31</x:v>
@@ -12037,7 +12045,9 @@
       <x:c r="I90" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J90" s="1"/>
+      <x:c r="J90" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K90" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -12118,23 +12128,23 @@
       <x:c r="A91" s="9">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="B91" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B91" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D91" s="1" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="D91" s="1" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="E91" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F91" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F91" s="1" t="s">
+      <x:c r="G91" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G91" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H91" s="1" t="s">
         <x:v>51</x:v>
@@ -12142,7 +12152,9 @@
       <x:c r="I91" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J91" s="1"/>
+      <x:c r="J91" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K91" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -12223,23 +12235,23 @@
       <x:c r="A92" s="9">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="B92" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B92" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="D92" s="1" t="s">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="D92" s="1" t="s">
-        <x:v>205</x:v>
-      </x:c>
       <x:c r="E92" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F92" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F92" s="1" t="s">
+      <x:c r="G92" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G92" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H92" s="1" t="s">
         <x:v>51</x:v>
@@ -12247,7 +12259,9 @@
       <x:c r="I92" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J92" s="1"/>
+      <x:c r="J92" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K92" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12328,23 +12342,23 @@
       <x:c r="A93" s="9">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B93" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B93" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D93" s="1" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="D93" s="1" t="s">
-        <x:v>207</x:v>
-      </x:c>
       <x:c r="E93" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F93" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F93" s="1" t="s">
+      <x:c r="G93" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G93" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H93" s="1" t="s">
         <x:v>31</x:v>
@@ -12352,7 +12366,9 @@
       <x:c r="I93" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J93" s="1"/>
+      <x:c r="J93" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K93" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12433,23 +12449,23 @@
       <x:c r="A94" s="9">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="B94" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B94" s="11" t="str">
+        <x:v>☐</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="D94" s="1" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="D94" s="1" t="s">
-        <x:v>209</x:v>
-      </x:c>
       <x:c r="E94" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F94" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F94" s="1" t="s">
+      <x:c r="G94" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G94" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H94" s="1" t="s">
         <x:v>31</x:v>
@@ -12457,7 +12473,9 @@
       <x:c r="I94" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J94" s="1"/>
+      <x:c r="J94" s="1" t="str">
+        <x:v>Sin perfil ADS personal guardado</x:v>
+      </x:c>
       <x:c r="K94" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12538,23 +12556,23 @@
       <x:c r="A95" s="9">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="B95" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B95" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="D95" s="1" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="D95" s="1" t="s">
-        <x:v>211</x:v>
-      </x:c>
       <x:c r="E95" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F95" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F95" s="1" t="s">
+      <x:c r="G95" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G95" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H95" s="1" t="s">
         <x:v>31</x:v>
@@ -12562,7 +12580,9 @@
       <x:c r="I95" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J95" s="1"/>
+      <x:c r="J95" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K95" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12643,23 +12663,23 @@
       <x:c r="A96" s="9">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B96" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B96" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D96" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="D96" s="1" t="s">
-        <x:v>213</x:v>
-      </x:c>
       <x:c r="E96" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F96" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F96" s="1" t="s">
+      <x:c r="G96" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G96" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H96" s="1" t="s">
         <x:v>31</x:v>
@@ -12667,7 +12687,9 @@
       <x:c r="I96" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J96" s="1"/>
+      <x:c r="J96" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K96" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12748,23 +12770,23 @@
       <x:c r="A97" s="9">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="B97" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B97" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="D97" s="1" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="D97" s="1" t="s">
-        <x:v>215</x:v>
-      </x:c>
       <x:c r="E97" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F97" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F97" s="1" t="s">
+      <x:c r="G97" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G97" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H97" s="1" t="s">
         <x:v>31</x:v>
@@ -12772,7 +12794,9 @@
       <x:c r="I97" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J97" s="1"/>
+      <x:c r="J97" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K97" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12853,23 +12877,23 @@
       <x:c r="A98" s="9">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B98" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B98" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="D98" s="1" t="s">
         <x:v>216</x:v>
       </x:c>
-      <x:c r="D98" s="1" t="s">
-        <x:v>217</x:v>
-      </x:c>
       <x:c r="E98" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F98" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F98" s="1" t="s">
+      <x:c r="G98" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G98" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H98" s="1" t="s">
         <x:v>31</x:v>
@@ -12877,7 +12901,9 @@
       <x:c r="I98" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J98" s="1"/>
+      <x:c r="J98" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K98" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -12958,23 +12984,23 @@
       <x:c r="A99" s="9">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="B99" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B99" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D99" s="1" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="D99" s="1" t="s">
-        <x:v>219</x:v>
-      </x:c>
       <x:c r="E99" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F99" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F99" s="1" t="s">
+      <x:c r="G99" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G99" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H99" s="1" t="s">
         <x:v>31</x:v>
@@ -12982,7 +13008,9 @@
       <x:c r="I99" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J99" s="1"/>
+      <x:c r="J99" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K99" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -13063,23 +13091,23 @@
       <x:c r="A100" s="9">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B100" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B100" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="D100" s="1" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="D100" s="1" t="s">
-        <x:v>221</x:v>
-      </x:c>
       <x:c r="E100" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F100" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F100" s="1" t="s">
+      <x:c r="G100" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G100" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H100" s="1" t="s">
         <x:v>31</x:v>
@@ -13087,7 +13115,9 @@
       <x:c r="I100" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J100" s="1"/>
+      <x:c r="J100" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K100" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -13168,23 +13198,23 @@
       <x:c r="A101" s="9">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="B101" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B101" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="D101" s="1" t="s">
-        <x:v>223</x:v>
-      </x:c>
       <x:c r="E101" s="13" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="F101" s="1" t="s">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="F101" s="1" t="s">
+      <x:c r="G101" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G101" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H101" s="1" t="s">
         <x:v>48</x:v>
@@ -13192,7 +13222,9 @@
       <x:c r="I101" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J101" s="1"/>
+      <x:c r="J101" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K101" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -13274,7 +13306,7 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B102" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
         <x:v>224</x:v>
@@ -13286,10 +13318,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G102" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G102" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H102" s="1" t="s">
         <x:v>31</x:v>
@@ -13379,7 +13411,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B103" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
         <x:v>227</x:v>
@@ -13391,10 +13423,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G103" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G103" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H103" s="1" t="s">
         <x:v>31</x:v>
@@ -13484,7 +13516,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B104" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
         <x:v>229</x:v>
@@ -13496,10 +13528,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G104" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G104" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H104" s="1" t="s">
         <x:v>51</x:v>
@@ -13589,7 +13621,7 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B105" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
         <x:v>231</x:v>
@@ -13601,10 +13633,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F105" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G105" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G105" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H105" s="1" t="s">
         <x:v>31</x:v>
@@ -13694,7 +13726,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B106" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
         <x:v>233</x:v>
@@ -13706,10 +13738,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G106" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G106" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H106" s="1" t="s">
         <x:v>31</x:v>
@@ -13799,7 +13831,7 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B107" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
         <x:v>235</x:v>
@@ -13811,10 +13843,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G107" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G107" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H107" s="1" t="s">
         <x:v>31</x:v>
@@ -13904,7 +13936,7 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B108" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
         <x:v>237</x:v>
@@ -13916,10 +13948,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G108" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G108" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H108" s="1" t="s">
         <x:v>31</x:v>
@@ -14009,7 +14041,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B109" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
         <x:v>239</x:v>
@@ -14021,10 +14053,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G109" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G109" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H109" s="1" t="s">
         <x:v>31</x:v>
@@ -14114,7 +14146,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B110" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
         <x:v>241</x:v>
@@ -14126,10 +14158,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F110" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G110" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G110" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H110" s="1" t="s">
         <x:v>51</x:v>
@@ -14219,7 +14251,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B111" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
         <x:v>243</x:v>
@@ -14231,10 +14263,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G111" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G111" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H111" s="1" t="s">
         <x:v>31</x:v>
@@ -14324,7 +14356,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B112" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
         <x:v>245</x:v>
@@ -14336,10 +14368,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G112" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G112" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H112" s="1" t="s">
         <x:v>31</x:v>
@@ -14429,7 +14461,7 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B113" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
         <x:v>247</x:v>
@@ -14441,10 +14473,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F113" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G113" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G113" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H113" s="1" t="s">
         <x:v>31</x:v>
@@ -14534,7 +14566,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B114" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
         <x:v>249</x:v>
@@ -14546,10 +14578,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G114" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G114" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H114" s="1" t="s">
         <x:v>31</x:v>
@@ -14638,8 +14670,8 @@
       <x:c r="A115" s="9">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="B115" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B115" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C115" s="1" t="s">
         <x:v>251</x:v>
@@ -14651,10 +14683,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F115" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G115" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G115" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H115" s="1" t="s">
         <x:v>31</x:v>
@@ -14662,7 +14694,9 @@
       <x:c r="I115" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J115" s="1"/>
+      <x:c r="J115" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K115" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -14743,8 +14777,8 @@
       <x:c r="A116" s="9">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="B116" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B116" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C116" s="1" t="s">
         <x:v>253</x:v>
@@ -14756,10 +14790,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F116" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G116" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G116" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H116" s="1" t="s">
         <x:v>31</x:v>
@@ -14767,7 +14801,9 @@
       <x:c r="I116" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J116" s="1"/>
+      <x:c r="J116" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K116" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -14848,8 +14884,8 @@
       <x:c r="A117" s="9">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="B117" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B117" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C117" s="1" t="s">
         <x:v>255</x:v>
@@ -14861,10 +14897,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F117" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G117" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G117" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H117" s="1" t="s">
         <x:v>31</x:v>
@@ -14872,7 +14908,9 @@
       <x:c r="I117" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J117" s="1"/>
+      <x:c r="J117" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K117" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -14953,8 +14991,8 @@
       <x:c r="A118" s="9">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B118" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B118" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C118" s="1" t="s">
         <x:v>257</x:v>
@@ -14966,10 +15004,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F118" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G118" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G118" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H118" s="1" t="s">
         <x:v>31</x:v>
@@ -14977,7 +15015,9 @@
       <x:c r="I118" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J118" s="1"/>
+      <x:c r="J118" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K118" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -15059,7 +15099,7 @@
         <x:v>113</x:v>
       </x:c>
       <x:c r="B119" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C119" s="1" t="s">
         <x:v>259</x:v>
@@ -15071,10 +15111,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F119" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G119" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G119" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H119" s="1" t="s">
         <x:v>31</x:v>
@@ -15164,7 +15204,7 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B120" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C120" s="1" t="s">
         <x:v>261</x:v>
@@ -15176,10 +15216,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F120" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G120" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G120" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H120" s="1" t="s">
         <x:v>51</x:v>
@@ -15269,7 +15309,7 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B121" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C121" s="1" t="s">
         <x:v>263</x:v>
@@ -15281,10 +15321,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F121" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G121" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G121" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H121" s="1" t="s">
         <x:v>48</x:v>
@@ -15373,8 +15413,8 @@
       <x:c r="A122" s="9">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="B122" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B122" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C122" s="1" t="s">
         <x:v>265</x:v>
@@ -15386,10 +15426,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F122" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G122" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G122" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H122" s="1" t="s">
         <x:v>31</x:v>
@@ -15397,7 +15437,9 @@
       <x:c r="I122" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J122" s="1"/>
+      <x:c r="J122" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K122" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -15479,7 +15521,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B123" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C123" s="1" t="s">
         <x:v>267</x:v>
@@ -15491,10 +15533,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F123" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G123" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G123" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H123" s="1" t="s">
         <x:v>31</x:v>
@@ -15584,7 +15626,7 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B124" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C124" s="1" t="s">
         <x:v>269</x:v>
@@ -15596,10 +15638,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F124" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G124" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G124" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H124" s="1" t="s">
         <x:v>31</x:v>
@@ -15689,7 +15731,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B125" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C125" s="1" t="s">
         <x:v>271</x:v>
@@ -15701,10 +15743,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F125" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G125" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G125" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H125" s="1" t="s">
         <x:v>31</x:v>
@@ -15793,8 +15835,8 @@
       <x:c r="A126" s="9">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="B126" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B126" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C126" s="1" t="s">
         <x:v>273</x:v>
@@ -15806,10 +15848,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F126" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G126" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G126" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H126" s="1" t="s">
         <x:v>51</x:v>
@@ -15817,7 +15859,9 @@
       <x:c r="I126" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J126" s="1"/>
+      <x:c r="J126" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K126" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -15899,7 +15943,7 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B127" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C127" s="1" t="s">
         <x:v>275</x:v>
@@ -15911,10 +15955,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F127" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G127" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G127" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H127" s="1" t="s">
         <x:v>51</x:v>
@@ -16004,7 +16048,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B128" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C128" s="1" t="s">
         <x:v>277</x:v>
@@ -16016,10 +16060,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F128" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G128" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G128" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H128" s="1" t="s">
         <x:v>51</x:v>
@@ -16109,7 +16153,7 @@
         <x:v>123</x:v>
       </x:c>
       <x:c r="B129" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C129" s="1" t="s">
         <x:v>279</x:v>
@@ -16121,10 +16165,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F129" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G129" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G129" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H129" s="1" t="s">
         <x:v>31</x:v>
@@ -16214,7 +16258,7 @@
         <x:v>124</x:v>
       </x:c>
       <x:c r="B130" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C130" s="1" t="s">
         <x:v>281</x:v>
@@ -16226,10 +16270,10 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="F130" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G130" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G130" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H130" s="1" t="s">
         <x:v>31</x:v>
@@ -16319,7 +16363,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B131" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C131" s="1" t="s">
         <x:v>283</x:v>
@@ -16331,10 +16375,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F131" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G131" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G131" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H131" s="1" t="s">
         <x:v>286</x:v>
@@ -16436,10 +16480,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F132" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G132" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G132" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H132" s="1" t="s">
         <x:v>289</x:v>
@@ -16543,10 +16587,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F133" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G133" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G133" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H133" s="1" t="s">
         <x:v>289</x:v>
@@ -16638,7 +16682,7 @@
         <x:v>128</x:v>
       </x:c>
       <x:c r="B134" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C134" s="1" t="s">
         <x:v>292</x:v>
@@ -16650,10 +16694,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F134" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G134" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G134" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H134" s="1" t="s">
         <x:v>289</x:v>
@@ -16743,7 +16787,7 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="B135" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C135" s="1" t="s">
         <x:v>294</x:v>
@@ -16755,10 +16799,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F135" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G135" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G135" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H135" s="1" t="s">
         <x:v>286</x:v>
@@ -16848,7 +16892,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="B136" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C136" s="1" t="s">
         <x:v>296</x:v>
@@ -16860,10 +16904,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F136" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G136" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G136" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H136" s="1" t="s">
         <x:v>298</x:v>
@@ -16953,7 +16997,7 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B137" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C137" s="1" t="s">
         <x:v>299</x:v>
@@ -16965,10 +17009,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F137" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G137" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G137" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H137" s="1" t="s">
         <x:v>289</x:v>
@@ -17058,7 +17102,7 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="B138" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C138" s="1" t="s">
         <x:v>301</x:v>
@@ -17070,10 +17114,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F138" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G138" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G138" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H138" s="1" t="s">
         <x:v>298</x:v>
@@ -17163,7 +17207,7 @@
         <x:v>133</x:v>
       </x:c>
       <x:c r="B139" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C139" s="1" t="s">
         <x:v>303</x:v>
@@ -17175,10 +17219,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F139" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G139" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G139" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H139" s="1" t="s">
         <x:v>298</x:v>
@@ -17268,7 +17312,7 @@
         <x:v>134</x:v>
       </x:c>
       <x:c r="B140" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C140" s="1" t="s">
         <x:v>305</x:v>
@@ -17280,10 +17324,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F140" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G140" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G140" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H140" s="1" t="s">
         <x:v>289</x:v>
@@ -17385,10 +17429,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F141" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G141" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G141" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H141" s="1" t="s">
         <x:v>298</x:v>
@@ -17480,7 +17524,7 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B142" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C142" s="1" t="s">
         <x:v>309</x:v>
@@ -17492,10 +17536,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F142" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G142" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G142" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H142" s="1" t="s">
         <x:v>289</x:v>
@@ -17597,10 +17641,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F143" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G143" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G143" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H143" s="1" t="s">
         <x:v>286</x:v>
@@ -17692,7 +17736,7 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B144" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C144" s="1" t="s">
         <x:v>313</x:v>
@@ -17704,10 +17748,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F144" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G144" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G144" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H144" s="1" t="s">
         <x:v>286</x:v>
@@ -17797,7 +17841,7 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B145" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C145" s="1" t="s">
         <x:v>315</x:v>
@@ -17809,10 +17853,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F145" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G145" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G145" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H145" s="1" t="s">
         <x:v>286</x:v>
@@ -17902,7 +17946,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B146" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C146" s="1" t="s">
         <x:v>316</x:v>
@@ -17914,10 +17958,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F146" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G146" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G146" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H146" s="1" t="s">
         <x:v>318</x:v>
@@ -18019,10 +18063,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F147" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G147" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G147" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H147" s="1" t="s">
         <x:v>298</x:v>
@@ -18126,10 +18170,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F148" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G148" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G148" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H148" s="1" t="s">
         <x:v>298</x:v>
@@ -18221,7 +18265,7 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B149" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C149" s="1" t="s">
         <x:v>323</x:v>
@@ -18233,10 +18277,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F149" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G149" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G149" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H149" s="1" t="s">
         <x:v>298</x:v>
@@ -18326,7 +18370,7 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B150" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C150" s="1" t="s">
         <x:v>325</x:v>
@@ -18338,10 +18382,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F150" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G150" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G150" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H150" s="1" t="s">
         <x:v>298</x:v>
@@ -18431,7 +18475,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B151" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C151" s="1" t="s">
         <x:v>327</x:v>
@@ -18443,10 +18487,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F151" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G151" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G151" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H151" s="1" t="s">
         <x:v>298</x:v>
@@ -18536,7 +18580,7 @@
         <x:v>146</x:v>
       </x:c>
       <x:c r="B152" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C152" s="1" t="s">
         <x:v>329</x:v>
@@ -18548,10 +18592,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F152" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G152" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G152" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H152" s="1" t="s">
         <x:v>289</x:v>
@@ -18641,7 +18685,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="B153" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C153" s="1" t="s">
         <x:v>331</x:v>
@@ -18653,10 +18697,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F153" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G153" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G153" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H153" s="1" t="s">
         <x:v>289</x:v>
@@ -18746,7 +18790,7 @@
         <x:v>148</x:v>
       </x:c>
       <x:c r="B154" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C154" s="1" t="s">
         <x:v>333</x:v>
@@ -18758,10 +18802,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F154" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G154" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G154" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H154" s="1" t="s">
         <x:v>335</x:v>
@@ -18863,10 +18907,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F155" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G155" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G155" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H155" s="1" t="s">
         <x:v>289</x:v>
@@ -18970,10 +19014,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F156" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G156" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G156" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H156" s="1" t="s">
         <x:v>289</x:v>
@@ -19065,7 +19109,7 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B157" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C157" s="1" t="s">
         <x:v>340</x:v>
@@ -19077,10 +19121,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F157" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G157" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G157" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H157" s="1" t="s">
         <x:v>289</x:v>
@@ -19170,7 +19214,7 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B158" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C158" s="1" t="s">
         <x:v>342</x:v>
@@ -19182,10 +19226,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F158" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G158" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G158" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H158" s="1" t="s">
         <x:v>289</x:v>
@@ -19275,7 +19319,7 @@
         <x:v>153</x:v>
       </x:c>
       <x:c r="B159" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C159" s="1" t="s">
         <x:v>344</x:v>
@@ -19287,10 +19331,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F159" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G159" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G159" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H159" s="1" t="s">
         <x:v>289</x:v>
@@ -19392,10 +19436,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F160" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G160" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G160" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H160" s="1" t="s">
         <x:v>153</x:v>
@@ -19487,7 +19531,7 @@
         <x:v>155</x:v>
       </x:c>
       <x:c r="B161" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C161" s="1" t="s">
         <x:v>348</x:v>
@@ -19499,10 +19543,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F161" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G161" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G161" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H161" s="1" t="s">
         <x:v>153</x:v>
@@ -19591,8 +19635,8 @@
       <x:c r="A162" s="9">
         <x:v>156</x:v>
       </x:c>
-      <x:c r="B162" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B162" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C162" s="1" t="s">
         <x:v>350</x:v>
@@ -19604,10 +19648,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F162" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G162" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G162" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H162" s="1" t="s">
         <x:v>289</x:v>
@@ -19615,7 +19659,9 @@
       <x:c r="I162" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J162" s="1"/>
+      <x:c r="J162" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K162" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -19697,7 +19743,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="B163" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C163" s="1" t="s">
         <x:v>352</x:v>
@@ -19709,10 +19755,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F163" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G163" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G163" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H163" s="1" t="s">
         <x:v>289</x:v>
@@ -19814,10 +19860,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F164" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G164" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G164" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H164" s="1" t="s">
         <x:v>289</x:v>
@@ -19909,7 +19955,7 @@
         <x:v>159</x:v>
       </x:c>
       <x:c r="B165" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C165" s="1" t="s">
         <x:v>356</x:v>
@@ -19921,10 +19967,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F165" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G165" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G165" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H165" s="1" t="s">
         <x:v>289</x:v>
@@ -20014,7 +20060,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="B166" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C166" s="1" t="s">
         <x:v>358</x:v>
@@ -20026,10 +20072,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F166" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G166" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G166" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H166" s="1" t="s">
         <x:v>318</x:v>
@@ -20119,7 +20165,7 @@
         <x:v>161</x:v>
       </x:c>
       <x:c r="B167" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C167" s="1" t="s">
         <x:v>360</x:v>
@@ -20131,10 +20177,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F167" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G167" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G167" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H167" s="1" t="s">
         <x:v>289</x:v>
@@ -20224,7 +20270,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="B168" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C168" s="1" t="s">
         <x:v>362</x:v>
@@ -20236,10 +20282,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F168" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G168" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G168" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H168" s="1" t="s">
         <x:v>289</x:v>
@@ -20329,7 +20375,7 @@
         <x:v>163</x:v>
       </x:c>
       <x:c r="B169" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C169" s="1" t="s">
         <x:v>364</x:v>
@@ -20341,10 +20387,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F169" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G169" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G169" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H169" s="1" t="s">
         <x:v>289</x:v>
@@ -20434,7 +20480,7 @@
         <x:v>164</x:v>
       </x:c>
       <x:c r="B170" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C170" s="1" t="s">
         <x:v>366</x:v>
@@ -20446,10 +20492,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F170" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G170" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G170" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H170" s="1" t="s">
         <x:v>289</x:v>
@@ -20539,7 +20585,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="B171" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C171" s="1" t="s">
         <x:v>368</x:v>
@@ -20551,10 +20597,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F171" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G171" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G171" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H171" s="1" t="s">
         <x:v>289</x:v>
@@ -20656,10 +20702,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F172" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G172" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G172" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H172" s="1" t="s">
         <x:v>289</x:v>
@@ -20751,7 +20797,7 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="B173" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C173" s="1" t="s">
         <x:v>372</x:v>
@@ -20763,10 +20809,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F173" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G173" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G173" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H173" s="1" t="s">
         <x:v>289</x:v>
@@ -20856,7 +20902,7 @@
         <x:v>168</x:v>
       </x:c>
       <x:c r="B174" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C174" s="1" t="s">
         <x:v>374</x:v>
@@ -20868,10 +20914,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F174" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G174" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G174" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H174" s="1" t="s">
         <x:v>289</x:v>
@@ -20973,10 +21019,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F175" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G175" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G175" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H175" s="1" t="s">
         <x:v>289</x:v>
@@ -21068,7 +21114,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="B176" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C176" s="1" t="s">
         <x:v>378</x:v>
@@ -21080,10 +21126,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F176" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G176" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G176" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H176" s="1" t="s">
         <x:v>289</x:v>
@@ -21173,7 +21219,7 @@
         <x:v>171</x:v>
       </x:c>
       <x:c r="B177" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C177" s="1" t="s">
         <x:v>380</x:v>
@@ -21185,10 +21231,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F177" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G177" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G177" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H177" s="1" t="s">
         <x:v>286</x:v>
@@ -21278,7 +21324,7 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="B178" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C178" s="1" t="s">
         <x:v>382</x:v>
@@ -21290,10 +21336,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F178" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G178" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G178" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H178" s="1" t="s">
         <x:v>289</x:v>
@@ -21383,7 +21429,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="B179" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C179" s="1" t="s">
         <x:v>384</x:v>
@@ -21395,10 +21441,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F179" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G179" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G179" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H179" s="1" t="s">
         <x:v>289</x:v>
@@ -21500,10 +21546,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F180" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G180" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G180" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H180" s="1" t="s">
         <x:v>289</x:v>
@@ -21595,7 +21641,7 @@
         <x:v>175</x:v>
       </x:c>
       <x:c r="B181" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C181" s="1" t="s">
         <x:v>388</x:v>
@@ -21607,10 +21653,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F181" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G181" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G181" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H181" s="1" t="s">
         <x:v>289</x:v>
@@ -21699,8 +21745,8 @@
       <x:c r="A182" s="9">
         <x:v>176</x:v>
       </x:c>
-      <x:c r="B182" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B182" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C182" s="1" t="s">
         <x:v>390</x:v>
@@ -21712,10 +21758,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F182" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G182" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G182" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H182" s="1" t="s">
         <x:v>289</x:v>
@@ -21723,7 +21769,9 @@
       <x:c r="I182" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J182" s="1"/>
+      <x:c r="J182" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K182" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -21805,7 +21853,7 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="B183" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C183" s="1" t="s">
         <x:v>392</x:v>
@@ -21817,10 +21865,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F183" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G183" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G183" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H183" s="1" t="s">
         <x:v>318</x:v>
@@ -21910,7 +21958,7 @@
         <x:v>178</x:v>
       </x:c>
       <x:c r="B184" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C184" s="1" t="s">
         <x:v>394</x:v>
@@ -21922,10 +21970,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F184" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G184" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G184" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H184" s="1" t="s">
         <x:v>298</x:v>
@@ -22015,7 +22063,7 @@
         <x:v>179</x:v>
       </x:c>
       <x:c r="B185" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C185" s="1" t="s">
         <x:v>396</x:v>
@@ -22027,10 +22075,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F185" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G185" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G185" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H185" s="1" t="s">
         <x:v>289</x:v>
@@ -22120,7 +22168,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="B186" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C186" s="1" t="s">
         <x:v>398</x:v>
@@ -22132,10 +22180,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F186" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G186" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G186" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H186" s="1" t="s">
         <x:v>298</x:v>
@@ -22225,7 +22273,7 @@
         <x:v>181</x:v>
       </x:c>
       <x:c r="B187" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C187" s="1" t="s">
         <x:v>400</x:v>
@@ -22237,10 +22285,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F187" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G187" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G187" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H187" s="1" t="s">
         <x:v>318</x:v>
@@ -22330,7 +22378,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="B188" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C188" s="1" t="s">
         <x:v>402</x:v>
@@ -22345,7 +22393,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G188" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H188" s="1" t="s">
         <x:v>318</x:v>
@@ -22435,7 +22483,7 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="B189" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C189" s="1" t="s">
         <x:v>404</x:v>
@@ -22450,7 +22498,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G189" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H189" s="1" t="s">
         <x:v>318</x:v>
@@ -22552,10 +22600,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F190" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G190" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G190" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H190" s="1" t="s">
         <x:v>298</x:v>
@@ -22647,7 +22695,7 @@
         <x:v>185</x:v>
       </x:c>
       <x:c r="B191" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C191" s="1" t="s">
         <x:v>408</x:v>
@@ -22659,10 +22707,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F191" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G191" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G191" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H191" s="1" t="s">
         <x:v>289</x:v>
@@ -22752,7 +22800,7 @@
         <x:v>186</x:v>
       </x:c>
       <x:c r="B192" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C192" s="1" t="s">
         <x:v>410</x:v>
@@ -22764,10 +22812,10 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="F192" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G192" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G192" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H192" s="1" t="s">
         <x:v>289</x:v>
@@ -22869,10 +22917,10 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="F193" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G193" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G193" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H193" s="1" t="s">
         <x:v>153</x:v>
@@ -22979,7 +23027,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G194" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H194" s="1" t="s">
         <x:v>153</x:v>
@@ -23083,10 +23131,10 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="F195" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G195" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G195" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H195" s="1" t="s">
         <x:v>153</x:v>
@@ -23284,8 +23332,8 @@
       <x:c r="A197" s="9">
         <x:v>191</x:v>
       </x:c>
-      <x:c r="B197" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B197" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C197" s="1" t="s">
         <x:v>421</x:v>
@@ -23308,7 +23356,9 @@
       <x:c r="I197" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J197" s="1"/>
+      <x:c r="J197" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K197" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -23390,7 +23440,7 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="B198" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C198" s="1" t="s">
         <x:v>423</x:v>
@@ -23495,7 +23545,7 @@
         <x:v>193</x:v>
       </x:c>
       <x:c r="B199" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C199" s="1" t="s">
         <x:v>426</x:v>
@@ -23600,7 +23650,7 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="B200" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C200" s="1" t="s">
         <x:v>428</x:v>
@@ -23705,7 +23755,7 @@
         <x:v>195</x:v>
       </x:c>
       <x:c r="B201" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C201" s="1" t="s">
         <x:v>430</x:v>
@@ -23720,7 +23770,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G201" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H201" s="1" t="s">
         <x:v>153</x:v>
@@ -23810,7 +23860,7 @@
         <x:v>196</x:v>
       </x:c>
       <x:c r="B202" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C202" s="1" t="s">
         <x:v>432</x:v>
@@ -23825,7 +23875,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G202" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H202" s="1" t="s">
         <x:v>153</x:v>
@@ -23915,7 +23965,7 @@
         <x:v>197</x:v>
       </x:c>
       <x:c r="B203" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C203" s="1" t="s">
         <x:v>434</x:v>
@@ -24019,8 +24069,8 @@
       <x:c r="A204" s="9">
         <x:v>198</x:v>
       </x:c>
-      <x:c r="B204" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B204" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C204" s="1" t="s">
         <x:v>437</x:v>
@@ -24035,7 +24085,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G204" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H204" s="1" t="s">
         <x:v>153</x:v>
@@ -24043,7 +24093,9 @@
       <x:c r="I204" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J204" s="1"/>
+      <x:c r="J204" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K204" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -24125,7 +24177,7 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="B205" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C205" s="1" t="s">
         <x:v>439</x:v>
@@ -24230,7 +24282,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="B206" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C206" s="1" t="s">
         <x:v>441</x:v>
@@ -24335,7 +24387,7 @@
         <x:v>201</x:v>
       </x:c>
       <x:c r="B207" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C207" s="1" t="s">
         <x:v>443</x:v>
@@ -24350,7 +24402,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G207" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H207" s="1" t="s">
         <x:v>153</x:v>
@@ -24440,7 +24492,7 @@
         <x:v>202</x:v>
       </x:c>
       <x:c r="B208" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C208" s="1" t="s">
         <x:v>445</x:v>
@@ -24651,8 +24703,8 @@
       <x:c r="A210" s="9">
         <x:v>204</x:v>
       </x:c>
-      <x:c r="B210" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B210" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C210" s="1" t="s">
         <x:v>449</x:v>
@@ -24675,7 +24727,9 @@
       <x:c r="I210" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J210" s="1"/>
+      <x:c r="J210" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K210" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -24757,7 +24811,7 @@
         <x:v>205</x:v>
       </x:c>
       <x:c r="B211" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C211" s="1" t="s">
         <x:v>451</x:v>
@@ -24862,7 +24916,7 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B212" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C212" s="1" t="s">
         <x:v>453</x:v>
@@ -24967,7 +25021,7 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B213" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C213" s="1" t="s">
         <x:v>455</x:v>
@@ -25072,7 +25126,7 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B214" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C214" s="1" t="s">
         <x:v>458</x:v>
@@ -25283,8 +25337,8 @@
       <x:c r="A216" s="9">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="B216" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B216" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C216" s="1" t="s">
         <x:v>462</x:v>
@@ -25299,7 +25353,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G216" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H216" s="1" t="s">
         <x:v>153</x:v>
@@ -25307,7 +25361,9 @@
       <x:c r="I216" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J216" s="1"/>
+      <x:c r="J216" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K216" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -25389,7 +25445,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B217" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C217" s="1" t="s">
         <x:v>464</x:v>
@@ -25494,7 +25550,7 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B218" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C218" s="1" t="s">
         <x:v>466</x:v>
@@ -25599,7 +25655,7 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B219" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C219" s="1" t="s">
         <x:v>468</x:v>
@@ -25611,10 +25667,10 @@
         <x:v>414</x:v>
       </x:c>
       <x:c r="F219" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G219" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G219" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H219" s="1" t="s">
         <x:v>153</x:v>
@@ -25719,7 +25775,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G220" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H220" s="1" t="s">
         <x:v>153</x:v>
@@ -25918,7 +25974,7 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="B222" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C222" s="1" t="s">
         <x:v>474</x:v>
@@ -26023,7 +26079,7 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B223" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C223" s="1" t="s">
         <x:v>476</x:v>
@@ -26128,7 +26184,7 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="B224" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C224" s="1" t="s">
         <x:v>478</x:v>
@@ -26233,7 +26289,7 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="B225" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C225" s="1" t="s">
         <x:v>480</x:v>
@@ -26338,7 +26394,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B226" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C226" s="1" t="s">
         <x:v>482</x:v>
@@ -26443,7 +26499,7 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B227" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C227" s="1" t="s">
         <x:v>484</x:v>
@@ -26548,7 +26604,7 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B228" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C228" s="1" t="s">
         <x:v>486</x:v>
@@ -26653,7 +26709,7 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B229" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C229" s="1" t="s">
         <x:v>488</x:v>
@@ -26758,7 +26814,7 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B230" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C230" s="1" t="s">
         <x:v>490</x:v>
@@ -26863,7 +26919,7 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="B231" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C231" s="1" t="s">
         <x:v>492</x:v>
@@ -26968,7 +27024,7 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B232" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C232" s="1" t="s">
         <x:v>494</x:v>
@@ -26983,7 +27039,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G232" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H232" s="1" t="s">
         <x:v>289</x:v>
@@ -27073,7 +27129,7 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="B233" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C233" s="1" t="s">
         <x:v>496</x:v>
@@ -27178,7 +27234,7 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="B234" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C234" s="1" t="s">
         <x:v>498</x:v>
@@ -27283,7 +27339,7 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B235" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C235" s="1" t="s">
         <x:v>500</x:v>
@@ -27388,7 +27444,7 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B236" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C236" s="1" t="s">
         <x:v>502</x:v>
@@ -27493,7 +27549,7 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="B237" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C237" s="1" t="s">
         <x:v>505</x:v>
@@ -27705,7 +27761,7 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B239" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C239" s="1" t="s">
         <x:v>509</x:v>
@@ -27810,7 +27866,7 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="B240" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C240" s="1" t="s">
         <x:v>511</x:v>
@@ -27915,7 +27971,7 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B241" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C241" s="1" t="s">
         <x:v>513</x:v>
@@ -28020,7 +28076,7 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B242" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C242" s="1" t="s">
         <x:v>516</x:v>
@@ -28125,7 +28181,7 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B243" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C243" s="1" t="s">
         <x:v>518</x:v>
@@ -28230,7 +28286,7 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B244" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C244" s="1" t="s">
         <x:v>520</x:v>
@@ -28549,7 +28605,7 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B247" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C247" s="1" t="s">
         <x:v>526</x:v>
@@ -28654,7 +28710,7 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B248" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C248" s="1" t="s">
         <x:v>529</x:v>
@@ -28759,7 +28815,7 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="B249" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C249" s="1" t="s">
         <x:v>531</x:v>
@@ -29077,8 +29133,8 @@
       <x:c r="A252" s="9">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="B252" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B252" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C252" s="1" t="s">
         <x:v>538</x:v>
@@ -29101,7 +29157,9 @@
       <x:c r="I252" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J252" s="1"/>
+      <x:c r="J252" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K252" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -29183,7 +29241,7 @@
         <x:v>247</x:v>
       </x:c>
       <x:c r="B253" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C253" s="1" t="s">
         <x:v>540</x:v>
@@ -29288,7 +29346,7 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="B254" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C254" s="1" t="s">
         <x:v>542</x:v>
@@ -29393,7 +29451,7 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="B255" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C255" s="1" t="s">
         <x:v>544</x:v>
@@ -29498,7 +29556,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="B256" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C256" s="1" t="s">
         <x:v>546</x:v>
@@ -29603,7 +29661,7 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="B257" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C257" s="1" t="s">
         <x:v>548</x:v>
@@ -29707,8 +29765,8 @@
       <x:c r="A258" s="9">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="B258" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B258" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C258" s="1" t="s">
         <x:v>550</x:v>
@@ -29731,7 +29789,9 @@
       <x:c r="I258" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J258" s="1"/>
+      <x:c r="J258" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K258" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -29920,7 +29980,7 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="B260" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C260" s="1" t="s">
         <x:v>554</x:v>
@@ -30025,7 +30085,7 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B261" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C261" s="1" t="s">
         <x:v>556</x:v>
@@ -30237,7 +30297,7 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="B263" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C263" s="1" t="s">
         <x:v>561</x:v>
@@ -30342,7 +30402,7 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B264" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C264" s="1" t="s">
         <x:v>563</x:v>
@@ -30447,7 +30507,7 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B265" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C265" s="1" t="s">
         <x:v>565</x:v>
@@ -30552,7 +30612,7 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="B266" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C266" s="1" t="s">
         <x:v>567</x:v>
@@ -30657,7 +30717,7 @@
         <x:v>261</x:v>
       </x:c>
       <x:c r="B267" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C267" s="1" t="s">
         <x:v>569</x:v>
@@ -30762,7 +30822,7 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B268" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C268" s="1" t="s">
         <x:v>571</x:v>
@@ -30867,7 +30927,7 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B269" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C269" s="1" t="s">
         <x:v>573</x:v>
@@ -30972,7 +31032,7 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B270" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C270" s="1" t="s">
         <x:v>576</x:v>
@@ -31077,7 +31137,7 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B271" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C271" s="1" t="s">
         <x:v>578</x:v>
@@ -31182,7 +31242,7 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="B272" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C272" s="1" t="s">
         <x:v>580</x:v>
@@ -31287,7 +31347,7 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B273" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C273" s="1" t="s">
         <x:v>582</x:v>
@@ -31392,7 +31452,7 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="B274" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C274" s="1" t="s">
         <x:v>584</x:v>
@@ -31497,7 +31557,7 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="B275" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C275" s="1" t="s">
         <x:v>586</x:v>
@@ -31602,7 +31662,7 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B276" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C276" s="1" t="s">
         <x:v>588</x:v>
@@ -31707,7 +31767,7 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="B277" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C277" s="1" t="s">
         <x:v>590</x:v>
@@ -31812,7 +31872,7 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="B278" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C278" s="1" t="s">
         <x:v>592</x:v>
@@ -31917,7 +31977,7 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B279" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C279" s="1" t="s">
         <x:v>594</x:v>
@@ -32022,7 +32082,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="B280" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C280" s="1" t="s">
         <x:v>596</x:v>
@@ -32127,7 +32187,7 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="B281" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C281" s="1" t="s">
         <x:v>598</x:v>
@@ -32139,10 +32199,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F281" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G281" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G281" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H281" s="1" t="s">
         <x:v>289</x:v>
@@ -32232,7 +32292,7 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B282" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C282" s="1" t="s">
         <x:v>601</x:v>
@@ -32244,10 +32304,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F282" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G282" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G282" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H282" s="1" t="s">
         <x:v>153</x:v>
@@ -32337,7 +32397,7 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B283" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C283" s="1" t="s">
         <x:v>603</x:v>
@@ -32349,10 +32409,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F283" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G283" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G283" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H283" s="1" t="s">
         <x:v>153</x:v>
@@ -32442,7 +32502,7 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="B284" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C284" s="1" t="s">
         <x:v>605</x:v>
@@ -32454,10 +32514,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F284" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G284" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G284" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H284" s="1" t="s">
         <x:v>289</x:v>
@@ -32547,7 +32607,7 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B285" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C285" s="1" t="s">
         <x:v>607</x:v>
@@ -32559,10 +32619,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F285" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G285" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G285" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H285" s="1" t="s">
         <x:v>436</x:v>
@@ -32652,7 +32712,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="B286" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C286" s="1" t="s">
         <x:v>609</x:v>
@@ -32664,10 +32724,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F286" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G286" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G286" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H286" s="1" t="s">
         <x:v>289</x:v>
@@ -32756,8 +32816,8 @@
       <x:c r="A287" s="9">
         <x:v>281</x:v>
       </x:c>
-      <x:c r="B287" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B287" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C287" s="1" t="s">
         <x:v>611</x:v>
@@ -32769,10 +32829,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F287" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G287" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G287" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H287" s="1" t="s">
         <x:v>153</x:v>
@@ -32780,7 +32840,9 @@
       <x:c r="I287" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J287" s="1"/>
+      <x:c r="J287" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K287" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -32861,8 +32923,8 @@
       <x:c r="A288" s="9">
         <x:v>282</x:v>
       </x:c>
-      <x:c r="B288" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B288" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C288" s="1" t="s">
         <x:v>613</x:v>
@@ -32874,10 +32936,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F288" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G288" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G288" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H288" s="1" t="s">
         <x:v>289</x:v>
@@ -32885,7 +32947,9 @@
       <x:c r="I288" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J288" s="1"/>
+      <x:c r="J288" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K288" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -32966,8 +33030,8 @@
       <x:c r="A289" s="9">
         <x:v>283</x:v>
       </x:c>
-      <x:c r="B289" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B289" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C289" s="1" t="s">
         <x:v>615</x:v>
@@ -32979,10 +33043,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F289" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G289" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G289" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H289" s="1" t="s">
         <x:v>153</x:v>
@@ -32990,7 +33054,9 @@
       <x:c r="I289" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J289" s="1"/>
+      <x:c r="J289" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K289" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -33072,7 +33138,7 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="B290" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C290" s="1" t="s">
         <x:v>617</x:v>
@@ -33084,10 +33150,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F290" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G290" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G290" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H290" s="1" t="s">
         <x:v>457</x:v>
@@ -33177,7 +33243,7 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="B291" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C291" s="1" t="s">
         <x:v>619</x:v>
@@ -33189,10 +33255,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F291" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G291" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G291" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H291" s="1" t="s">
         <x:v>153</x:v>
@@ -33282,7 +33348,7 @@
         <x:v>286</x:v>
       </x:c>
       <x:c r="B292" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C292" s="1" t="s">
         <x:v>621</x:v>
@@ -33294,10 +33360,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F292" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G292" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G292" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H292" s="1" t="s">
         <x:v>436</x:v>
@@ -33387,7 +33453,7 @@
         <x:v>287</x:v>
       </x:c>
       <x:c r="B293" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C293" s="1" t="s">
         <x:v>623</x:v>
@@ -33399,10 +33465,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F293" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G293" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G293" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H293" s="1" t="s">
         <x:v>153</x:v>
@@ -33492,7 +33558,7 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B294" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C294" s="1" t="s">
         <x:v>625</x:v>
@@ -33504,10 +33570,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F294" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G294" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G294" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H294" s="1" t="s">
         <x:v>289</x:v>
@@ -33597,7 +33663,7 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="B295" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C295" s="1" t="s">
         <x:v>627</x:v>
@@ -33609,10 +33675,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F295" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G295" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G295" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H295" s="1" t="s">
         <x:v>289</x:v>
@@ -33702,7 +33768,7 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="B296" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C296" s="1" t="s">
         <x:v>629</x:v>
@@ -33714,10 +33780,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F296" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G296" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G296" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H296" s="1" t="s">
         <x:v>335</x:v>
@@ -33807,7 +33873,7 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B297" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C297" s="1" t="s">
         <x:v>631</x:v>
@@ -33819,10 +33885,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F297" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G297" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G297" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H297" s="1" t="s">
         <x:v>335</x:v>
@@ -33912,7 +33978,7 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="B298" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C298" s="1" t="s">
         <x:v>633</x:v>
@@ -33924,10 +33990,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F298" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G298" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G298" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H298" s="1" t="s">
         <x:v>289</x:v>
@@ -34017,7 +34083,7 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="B299" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C299" s="1" t="s">
         <x:v>635</x:v>
@@ -34029,10 +34095,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F299" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G299" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G299" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H299" s="1" t="s">
         <x:v>298</x:v>
@@ -34121,8 +34187,8 @@
       <x:c r="A300" s="9">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="B300" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B300" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C300" s="1" t="s">
         <x:v>637</x:v>
@@ -34134,10 +34200,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F300" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G300" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G300" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H300" s="1" t="s">
         <x:v>298</x:v>
@@ -34145,7 +34211,9 @@
       <x:c r="I300" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J300" s="1"/>
+      <x:c r="J300" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K300" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -34226,8 +34294,8 @@
       <x:c r="A301" s="9">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="B301" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B301" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C301" s="1" t="s">
         <x:v>639</x:v>
@@ -34239,10 +34307,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F301" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G301" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G301" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H301" s="1" t="s">
         <x:v>298</x:v>
@@ -34250,7 +34318,9 @@
       <x:c r="I301" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J301" s="1"/>
+      <x:c r="J301" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K301" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -34331,8 +34401,8 @@
       <x:c r="A302" s="9">
         <x:v>296</x:v>
       </x:c>
-      <x:c r="B302" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B302" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C302" s="1" t="s">
         <x:v>641</x:v>
@@ -34344,10 +34414,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F302" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G302" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G302" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H302" s="1" t="s">
         <x:v>298</x:v>
@@ -34355,7 +34425,9 @@
       <x:c r="I302" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J302" s="1"/>
+      <x:c r="J302" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K302" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -34437,7 +34509,7 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="B303" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C303" s="1" t="s">
         <x:v>643</x:v>
@@ -34449,10 +34521,10 @@
         <x:v>600</x:v>
       </x:c>
       <x:c r="F303" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G303" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G303" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H303" s="1" t="s">
         <x:v>289</x:v>
@@ -34542,7 +34614,7 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B304" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C304" s="1" t="s">
         <x:v>645</x:v>
@@ -34647,7 +34719,7 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B305" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C305" s="1" t="s">
         <x:v>648</x:v>
@@ -34752,7 +34824,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="B306" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C306" s="1" t="s">
         <x:v>650</x:v>
@@ -34857,7 +34929,7 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B307" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C307" s="1" t="s">
         <x:v>652</x:v>
@@ -34962,7 +35034,7 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="B308" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C308" s="1" t="s">
         <x:v>654</x:v>
@@ -35067,7 +35139,7 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="B309" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C309" s="1" t="s">
         <x:v>656</x:v>
@@ -35172,7 +35244,7 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B310" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C310" s="1" t="s">
         <x:v>658</x:v>
@@ -35276,8 +35348,8 @@
       <x:c r="A311" s="9">
         <x:v>305</x:v>
       </x:c>
-      <x:c r="B311" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B311" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C311" s="1" t="s">
         <x:v>660</x:v>
@@ -35300,7 +35372,9 @@
       <x:c r="I311" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J311" s="1"/>
+      <x:c r="J311" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K311" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -35381,8 +35455,8 @@
       <x:c r="A312" s="9">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="B312" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B312" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C312" s="1" t="s">
         <x:v>662</x:v>
@@ -35405,7 +35479,9 @@
       <x:c r="I312" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J312" s="1"/>
+      <x:c r="J312" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K312" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -35487,7 +35563,7 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B313" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C313" s="1" t="s">
         <x:v>664</x:v>
@@ -35592,7 +35668,7 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="B314" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C314" s="1" t="s">
         <x:v>666</x:v>
@@ -35696,8 +35772,8 @@
       <x:c r="A315" s="9">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="B315" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B315" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C315" s="1" t="s">
         <x:v>668</x:v>
@@ -35720,7 +35796,9 @@
       <x:c r="I315" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J315" s="1"/>
+      <x:c r="J315" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K315" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -35802,7 +35880,7 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B316" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C316" s="1" t="s">
         <x:v>670</x:v>
@@ -35906,8 +35984,8 @@
       <x:c r="A317" s="9">
         <x:v>311</x:v>
       </x:c>
-      <x:c r="B317" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B317" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C317" s="1" t="s">
         <x:v>672</x:v>
@@ -35930,7 +36008,9 @@
       <x:c r="I317" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J317" s="1"/>
+      <x:c r="J317" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K317" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -36012,7 +36092,7 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="B318" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C318" s="1" t="s">
         <x:v>674</x:v>
@@ -36117,7 +36197,7 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="B319" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C319" s="1" t="s">
         <x:v>676</x:v>
@@ -36222,7 +36302,7 @@
         <x:v>314</x:v>
       </x:c>
       <x:c r="B320" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C320" s="1" t="s">
         <x:v>679</x:v>
@@ -36326,8 +36406,8 @@
       <x:c r="A321" s="9">
         <x:v>315</x:v>
       </x:c>
-      <x:c r="B321" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B321" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C321" s="1" t="s">
         <x:v>680</x:v>
@@ -36350,7 +36430,9 @@
       <x:c r="I321" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J321" s="1"/>
+      <x:c r="J321" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K321" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -36431,8 +36513,8 @@
       <x:c r="A322" s="9">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="B322" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B322" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C322" s="1" t="s">
         <x:v>682</x:v>
@@ -36455,7 +36537,9 @@
       <x:c r="I322" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J322" s="1"/>
+      <x:c r="J322" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K322" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -36537,7 +36621,7 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B323" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C323" s="1" t="s">
         <x:v>684</x:v>
@@ -36642,7 +36726,7 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="B324" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C324" s="1" t="s">
         <x:v>687</x:v>
@@ -36746,8 +36830,8 @@
       <x:c r="A325" s="9">
         <x:v>319</x:v>
       </x:c>
-      <x:c r="B325" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B325" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C325" s="1" t="s">
         <x:v>688</x:v>
@@ -36770,7 +36854,9 @@
       <x:c r="I325" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J325" s="1"/>
+      <x:c r="J325" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K325" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -36851,8 +36937,8 @@
       <x:c r="A326" s="9">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="B326" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B326" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C326" s="1" t="s">
         <x:v>690</x:v>
@@ -36875,7 +36961,9 @@
       <x:c r="I326" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J326" s="1"/>
+      <x:c r="J326" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K326" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -36957,7 +37045,7 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B327" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C327" s="1" t="s">
         <x:v>692</x:v>
@@ -37062,7 +37150,7 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="B328" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C328" s="1" t="s">
         <x:v>694</x:v>
@@ -37167,7 +37255,7 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B329" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C329" s="1" t="s">
         <x:v>695</x:v>
@@ -37272,7 +37360,7 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="B330" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C330" s="1" t="s">
         <x:v>697</x:v>
@@ -37377,7 +37465,7 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="B331" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C331" s="1" t="s">
         <x:v>698</x:v>
@@ -37482,7 +37570,7 @@
         <x:v>326</x:v>
       </x:c>
       <x:c r="B332" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C332" s="1" t="s">
         <x:v>700</x:v>
@@ -37587,7 +37675,7 @@
         <x:v>327</x:v>
       </x:c>
       <x:c r="B333" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C333" s="1" t="s">
         <x:v>702</x:v>
@@ -37692,7 +37780,7 @@
         <x:v>328</x:v>
       </x:c>
       <x:c r="B334" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C334" s="1" t="s">
         <x:v>704</x:v>
@@ -37797,7 +37885,7 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="B335" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C335" s="1" t="s">
         <x:v>705</x:v>
@@ -37902,7 +37990,7 @@
         <x:v>330</x:v>
       </x:c>
       <x:c r="B336" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C336" s="1" t="s">
         <x:v>707</x:v>
@@ -38007,7 +38095,7 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="B337" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C337" s="1" t="s">
         <x:v>709</x:v>
@@ -38112,7 +38200,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="B338" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C338" s="1" t="s">
         <x:v>711</x:v>
@@ -38217,7 +38305,7 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="B339" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C339" s="1" t="s">
         <x:v>713</x:v>
@@ -38322,7 +38410,7 @@
         <x:v>334</x:v>
       </x:c>
       <x:c r="B340" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C340" s="1" t="s">
         <x:v>715</x:v>
@@ -38427,7 +38515,7 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="B341" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C341" s="1" t="s">
         <x:v>717</x:v>
@@ -38531,8 +38619,8 @@
       <x:c r="A342" s="9">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="B342" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B342" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C342" s="1" t="s">
         <x:v>719</x:v>
@@ -38555,7 +38643,9 @@
       <x:c r="I342" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J342" s="1"/>
+      <x:c r="J342" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K342" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -38636,8 +38726,8 @@
       <x:c r="A343" s="9">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="B343" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B343" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C343" s="1" t="s">
         <x:v>721</x:v>
@@ -38652,7 +38742,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G343" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H343" s="1" t="s">
         <x:v>102</x:v>
@@ -38660,7 +38750,9 @@
       <x:c r="I343" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J343" s="1"/>
+      <x:c r="J343" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K343" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -38742,7 +38834,7 @@
         <x:v>338</x:v>
       </x:c>
       <x:c r="B344" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C344" s="1" t="s">
         <x:v>724</x:v>
@@ -38757,7 +38849,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G344" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H344" s="1" t="s">
         <x:v>102</x:v>
@@ -38847,7 +38939,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="B345" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C345" s="1" t="s">
         <x:v>726</x:v>
@@ -38862,7 +38954,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G345" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H345" s="1" t="s">
         <x:v>102</x:v>
@@ -38952,7 +39044,7 @@
         <x:v>340</x:v>
       </x:c>
       <x:c r="B346" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C346" s="1" t="s">
         <x:v>728</x:v>
@@ -38967,7 +39059,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G346" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H346" s="1" t="s">
         <x:v>102</x:v>
@@ -39057,7 +39149,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="B347" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C347" s="1" t="s">
         <x:v>729</x:v>
@@ -39072,7 +39164,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G347" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H347" s="1" t="s">
         <x:v>102</x:v>
@@ -39162,7 +39254,7 @@
         <x:v>342</x:v>
       </x:c>
       <x:c r="B348" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C348" s="1" t="s">
         <x:v>731</x:v>
@@ -39177,7 +39269,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G348" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H348" s="1" t="s">
         <x:v>102</x:v>
@@ -39267,7 +39359,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="B349" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C349" s="1" t="s">
         <x:v>733</x:v>
@@ -39282,7 +39374,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G349" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="H349" s="1" t="s">
         <x:v>102</x:v>
@@ -39372,7 +39464,7 @@
         <x:v>344</x:v>
       </x:c>
       <x:c r="B350" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C350" s="1" t="s">
         <x:v>735</x:v>
@@ -39477,7 +39569,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="B351" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C351" s="1" t="s">
         <x:v>739</x:v>
@@ -39582,7 +39674,7 @@
         <x:v>346</x:v>
       </x:c>
       <x:c r="B352" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C352" s="1" t="s">
         <x:v>742</x:v>
@@ -39687,7 +39779,7 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="B353" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C353" s="1" t="s">
         <x:v>744</x:v>
@@ -39792,7 +39884,7 @@
         <x:v>348</x:v>
       </x:c>
       <x:c r="B354" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
         <x:v>746</x:v>
@@ -39897,7 +39989,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="B355" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
         <x:v>749</x:v>
@@ -40002,7 +40094,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="B356" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
         <x:v>751</x:v>
@@ -40014,7 +40106,7 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F356" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G356" s="1" t="s">
         <x:v>123</x:v>
@@ -40107,7 +40199,7 @@
         <x:v>351</x:v>
       </x:c>
       <x:c r="B357" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
         <x:v>753</x:v>
@@ -40119,7 +40211,7 @@
         <x:v>737</x:v>
       </x:c>
       <x:c r="F357" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G357" s="1" t="s">
         <x:v>123</x:v>
@@ -40212,7 +40304,7 @@
         <x:v>352</x:v>
       </x:c>
       <x:c r="B358" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C358" s="1" t="s">
         <x:v>755</x:v>
@@ -40317,7 +40409,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="B359" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C359" s="1" t="s">
         <x:v>757</x:v>
@@ -40422,7 +40514,7 @@
         <x:v>354</x:v>
       </x:c>
       <x:c r="B360" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C360" s="1" t="s">
         <x:v>759</x:v>
@@ -40527,7 +40619,7 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="B361" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
         <x:v>761</x:v>
@@ -40631,8 +40723,8 @@
       <x:c r="A362" s="9">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="B362" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B362" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C362" s="1" t="s">
         <x:v>763</x:v>
@@ -40655,7 +40747,9 @@
       <x:c r="I362" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J362" s="1"/>
+      <x:c r="J362" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K362" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -40737,7 +40831,7 @@
         <x:v>357</x:v>
       </x:c>
       <x:c r="B363" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C363" s="1" t="s">
         <x:v>765</x:v>
@@ -40842,7 +40936,7 @@
         <x:v>358</x:v>
       </x:c>
       <x:c r="B364" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C364" s="1" t="s">
         <x:v>767</x:v>
@@ -40946,8 +41040,8 @@
       <x:c r="A365" s="9">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="B365" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B365" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C365" s="1" t="s">
         <x:v>769</x:v>
@@ -40970,7 +41064,9 @@
       <x:c r="I365" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J365" s="1"/>
+      <x:c r="J365" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K365" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -41052,7 +41148,7 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="B366" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C366" s="1" t="s">
         <x:v>774</x:v>
@@ -41156,8 +41252,8 @@
       <x:c r="A367" s="9">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="B367" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B367" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C367" s="1" t="s">
         <x:v>775</x:v>
@@ -41180,7 +41276,9 @@
       <x:c r="I367" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J367" s="1"/>
+      <x:c r="J367" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K367" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -41261,8 +41359,8 @@
       <x:c r="A368" s="9">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="B368" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B368" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C368" s="1" t="s">
         <x:v>777</x:v>
@@ -41285,7 +41383,9 @@
       <x:c r="I368" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J368" s="1"/>
+      <x:c r="J368" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K368" s="24" t="str">
         <x:v>No aplica</x:v>
       </x:c>
@@ -41367,7 +41467,7 @@
         <x:v>363</x:v>
       </x:c>
       <x:c r="B369" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C369" s="1" t="s">
         <x:v>778</x:v>
@@ -41472,7 +41572,7 @@
         <x:v>364</x:v>
       </x:c>
       <x:c r="B370" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C370" s="1" t="s">
         <x:v>779</x:v>
@@ -41576,8 +41676,8 @@
       <x:c r="A371" s="9">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="B371" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B371" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C371" s="1" t="s">
         <x:v>783</x:v>
@@ -41600,7 +41700,9 @@
       <x:c r="I371" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J371" s="1"/>
+      <x:c r="J371" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K371" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -41681,8 +41783,8 @@
       <x:c r="A372" s="9">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="B372" s="11" t="s">
-        <x:v>188</x:v>
+      <x:c r="B372" s="11" t="str">
+        <x:v>☑</x:v>
       </x:c>
       <x:c r="C372" s="1" t="s">
         <x:v>787</x:v>
@@ -41705,7 +41807,9 @@
       <x:c r="I372" s="10" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="J372" s="1"/>
+      <x:c r="J372" s="1" t="str">
+        <x:v>Mira de hierro calibrada manualmente</x:v>
+      </x:c>
       <x:c r="K372" s="24" t="str">
         <x:v>☐</x:v>
       </x:c>
@@ -41787,7 +41891,7 @@
         <x:v>367</x:v>
       </x:c>
       <x:c r="B373" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C373" s="1" t="s">
         <x:v>789</x:v>
@@ -41892,7 +41996,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="B374" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C374" s="1" t="s">
         <x:v>791</x:v>
@@ -41997,7 +42101,7 @@
         <x:v>369</x:v>
       </x:c>
       <x:c r="B375" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C375" s="1" t="s">
         <x:v>793</x:v>
@@ -42102,7 +42206,7 @@
         <x:v>370</x:v>
       </x:c>
       <x:c r="B376" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C376" s="1" t="s">
         <x:v>795</x:v>
@@ -42207,7 +42311,7 @@
         <x:v>371</x:v>
       </x:c>
       <x:c r="B377" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C377" s="1" t="s">
         <x:v>797</x:v>
@@ -42312,7 +42416,7 @@
         <x:v>372</x:v>
       </x:c>
       <x:c r="B378" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C378" s="1" t="s">
         <x:v>800</x:v>
@@ -42417,7 +42521,7 @@
         <x:v>373</x:v>
       </x:c>
       <x:c r="B379" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C379" s="1" t="s">
         <x:v>802</x:v>
@@ -42522,7 +42626,7 @@
         <x:v>374</x:v>
       </x:c>
       <x:c r="B380" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C380" s="1" t="s">
         <x:v>804</x:v>
@@ -42534,10 +42638,10 @@
         <x:v>799</x:v>
       </x:c>
       <x:c r="F380" s="1" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G380" s="1" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="G380" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="H380" s="1" t="s">
         <x:v>806</x:v>
@@ -42627,7 +42731,7 @@
         <x:v>375</x:v>
       </x:c>
       <x:c r="B381" s="11" t="s">
-        <x:v>188</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C381" s="1" t="s">
         <x:v>807</x:v>
@@ -42750,7 +42854,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4579a698538345c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab57072c66714c1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>